--- a/output/yearly_surface_area_iteration_73_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_73_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497621065811</v>
+        <v>10.84497646523778</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907151834708</v>
+        <v>37.78907240542412</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.899321954819084</v>
+        <v>5.285729639664827</v>
       </c>
       <c r="C2" t="n">
-        <v>9.967684441217866</v>
+        <v>4.2784564951076</v>
       </c>
       <c r="D2" t="n">
-        <v>38.09966490641022</v>
+        <v>21.34515858573415</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.58234061953438</v>
+        <v>14.87838645786041</v>
       </c>
       <c r="C3" t="n">
-        <v>38.0574497551276</v>
+        <v>22.09423208407447</v>
       </c>
       <c r="D3" t="n">
-        <v>90.56131697824702</v>
+        <v>80.63093894979055</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.50588747179015</v>
+        <v>32.64703815702343</v>
       </c>
       <c r="C4" t="n">
-        <v>90.84504206477436</v>
+        <v>66.91494177375834</v>
       </c>
       <c r="D4" t="n">
-        <v>107.8832734719777</v>
+        <v>114.9665831581185</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.31961744989052</v>
+        <v>39.29445186247859</v>
       </c>
       <c r="C5" t="n">
-        <v>117.5888312761617</v>
+        <v>112.7046364475339</v>
       </c>
       <c r="D5" t="n">
-        <v>79.10432126968676</v>
+        <v>81.48505945248527</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.06927178530758</v>
+        <v>36.46800022195202</v>
       </c>
       <c r="C6" t="n">
-        <v>122.0430206103295</v>
+        <v>113.751179500261</v>
       </c>
       <c r="D6" t="n">
-        <v>51.64287448649497</v>
+        <v>52.1258943569844</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.73990327829938</v>
+        <v>26.58965482182061</v>
       </c>
       <c r="C7" t="n">
-        <v>102.7654226897391</v>
+        <v>80.42771717501144</v>
       </c>
       <c r="D7" t="n">
-        <v>39.64493579289469</v>
+        <v>40.42346172236242</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.6062624173348</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>65.34021845614646</v>
+        <v>46.56429361242621</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>37.71874679716245</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.50155957034565</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>28.75539025738908</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.67528785626833</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.668415573864112</v>
+        <v>7.699183547094685</v>
       </c>
       <c r="C21" t="n">
-        <v>93.93809077983536</v>
+        <v>94.31499845190987</v>
       </c>
       <c r="D21" t="n">
-        <v>7.668415573864112</v>
+        <v>8.66158149048152</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.178539213452678</v>
+        <v>5.255295460833175</v>
       </c>
       <c r="C2" t="n">
-        <v>7.523132657643308</v>
+        <v>14.61625982082651</v>
       </c>
       <c r="D2" t="n">
-        <v>40.29976151162732</v>
+        <v>30.83964063350506</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.95893082733765</v>
+        <v>16.22828955119978</v>
       </c>
       <c r="C3" t="n">
-        <v>38.13598957146735</v>
+        <v>19.11953654020664</v>
       </c>
       <c r="D3" t="n">
-        <v>97.40900721536853</v>
+        <v>78.76070957320036</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.68005772606933</v>
+        <v>30.24764676784423</v>
       </c>
       <c r="C4" t="n">
-        <v>91.81500879657021</v>
+        <v>60.87817514034472</v>
       </c>
       <c r="D4" t="n">
-        <v>123.1602494977624</v>
+        <v>125.8148952900457</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.49204519293946</v>
+        <v>43.71231653158924</v>
       </c>
       <c r="C5" t="n">
-        <v>140.9053392520235</v>
+        <v>116.7788894201581</v>
       </c>
       <c r="D5" t="n">
-        <v>96.40762455703681</v>
+        <v>101.7826932377881</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.39507315439728</v>
+        <v>44.67933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>150.2594313780871</v>
+        <v>145.3487293614446</v>
       </c>
       <c r="D6" t="n">
-        <v>61.66553679915066</v>
+        <v>63.3963580017378</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.36357511240336</v>
+        <v>34.49468733641593</v>
       </c>
       <c r="C7" t="n">
-        <v>136.6612439265645</v>
+        <v>119.5935600882337</v>
       </c>
       <c r="D7" t="n">
-        <v>44.67541102945535</v>
+        <v>45.8132566186774</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.36697801940583</v>
+        <v>21.02903582496668</v>
       </c>
       <c r="C8" t="n">
-        <v>96.71687508387453</v>
+        <v>75.35404503946393</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.63668090063322</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.75937400146829</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>57.35468262980289</v>
+        <v>43.26562132615692</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>36.16562192904399</v>
       </c>
     </row>
     <row r="10">
@@ -1206,7 +1206,7 @@
         <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>36.44247478164161</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
         <v>35.3036474447153</v>
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
         <v>31.8076438698924</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.840848361535177</v>
+        <v>7.88327797516992</v>
       </c>
       <c r="C21" t="n">
-        <v>101.9310286999573</v>
+        <v>103.4680234241052</v>
       </c>
       <c r="D21" t="n">
-        <v>8.820954406727076</v>
+        <v>9.854097468962401</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.928193548869741</v>
+        <v>7.211918635397069</v>
       </c>
       <c r="C2" t="n">
-        <v>9.634871969478198</v>
+        <v>16.66025854106837</v>
       </c>
       <c r="D2" t="n">
-        <v>34.32386323587698</v>
+        <v>41.75863860013808</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.21556788877357</v>
+        <v>16.63080610994097</v>
       </c>
       <c r="C3" t="n">
-        <v>33.80648219573892</v>
+        <v>36.80081269369169</v>
       </c>
       <c r="D3" t="n">
-        <v>103.6627400914207</v>
+        <v>83.24729658160828</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.22059980048183</v>
+        <v>30.24764676784423</v>
       </c>
       <c r="C4" t="n">
-        <v>92.04473775936395</v>
+        <v>54.08840801777377</v>
       </c>
       <c r="D4" t="n">
-        <v>138.1436829599772</v>
+        <v>134.1106633909313</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.99550183876883</v>
+        <v>44.17864669110647</v>
       </c>
       <c r="C5" t="n">
-        <v>150.9927969131595</v>
+        <v>113.3427724552943</v>
       </c>
       <c r="D5" t="n">
-        <v>111.4038207394068</v>
+        <v>117.8833555874358</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.62778841803278</v>
+        <v>50.67683474551611</v>
       </c>
       <c r="C6" t="n">
-        <v>179.2808752633271</v>
+        <v>163.5022261606723</v>
       </c>
       <c r="D6" t="n">
-        <v>73.82153687313468</v>
+        <v>77.4441859018054</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>48.20872101703962</v>
+        <v>42.51949307092936</v>
       </c>
       <c r="C7" t="n">
-        <v>170.6169517733489</v>
+        <v>158.1006502919063</v>
       </c>
       <c r="D7" t="n">
-        <v>49.76577287597506</v>
+        <v>51.50248456478767</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>32.3780392860598</v>
+        <v>28.28906009787184</v>
       </c>
       <c r="C8" t="n">
-        <v>130.5969883574319</v>
+        <v>111.9879606234336</v>
       </c>
       <c r="D8" t="n">
-        <v>40.22220344299182</v>
+        <v>41.64082887562846</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.64062358698343</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>82.53749299143782</v>
+        <v>64.5656195174957</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>37.27499683484289</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>49.39663573917827</v>
+        <v>40.85543071223102</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.00617789032851</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.9962136553292</v>
+        <v>8.051585685354732</v>
       </c>
       <c r="C21" t="n">
-        <v>108.9484110538603</v>
+        <v>111.7157513842969</v>
       </c>
       <c r="D21" t="n">
-        <v>9.9952670691615</v>
+        <v>11.07093031736276</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.525676990128549</v>
+        <v>6.48542533425443</v>
       </c>
       <c r="C2" t="n">
-        <v>6.705336820005715</v>
+        <v>11.32838675930394</v>
       </c>
       <c r="D2" t="n">
-        <v>28.45399371218531</v>
+        <v>34.04602863557513</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.06401888942107</v>
+        <v>20.53816197284327</v>
       </c>
       <c r="C3" t="n">
-        <v>52.75421288770235</v>
+        <v>53.711416899343</v>
       </c>
       <c r="D3" t="n">
-        <v>110.8589507635498</v>
+        <v>92.06829970426588</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.01943933210246</v>
+        <v>21.22440361811179</v>
       </c>
       <c r="C4" t="n">
-        <v>123.9643008675405</v>
+        <v>86.68439529417637</v>
       </c>
       <c r="D4" t="n">
-        <v>130.2180337435927</v>
+        <v>131.2007631955437</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.31775176547326</v>
+        <v>28.54431450097602</v>
       </c>
       <c r="C5" t="n">
-        <v>107.108674533327</v>
+        <v>97.68389657255766</v>
       </c>
       <c r="D5" t="n">
-        <v>74.04832059281568</v>
+        <v>77.95076771719675</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.90698031447059</v>
+        <v>26.40508625342222</v>
       </c>
       <c r="C6" t="n">
-        <v>112.3826232005409</v>
+        <v>104.1310337463464</v>
       </c>
       <c r="D6" t="n">
-        <v>32.76484788153306</v>
+        <v>33.89189424600839</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.43940636534185</v>
+        <v>18.74450891718435</v>
       </c>
       <c r="C7" t="n">
-        <v>91.80617306723197</v>
+        <v>78.75089209615788</v>
       </c>
       <c r="D7" t="n">
-        <v>28.26647990067416</v>
+        <v>29.2845522699781</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.51590057081509</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>60.8339964936536</v>
+        <v>47.56567627075796</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>27.45457454926205</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>37.71874679716245</v>
+        <v>31.17343485294896</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.62343515439249</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>28.04362317181014</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.60910984945629</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>26.90381408717959</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>23.96838845148163</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>74.64718669240621</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.190099201725387</v>
+        <v>3.861213720802705</v>
       </c>
       <c r="C2" t="n">
-        <v>3.199515768140355</v>
+        <v>5.408448102695679</v>
       </c>
       <c r="D2" t="n">
-        <v>20.92398882061227</v>
+        <v>23.29687302177681</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.48478774391545</v>
+        <v>22.00587479069226</v>
       </c>
       <c r="C3" t="n">
-        <v>40.25165587411922</v>
+        <v>49.85805716017427</v>
       </c>
       <c r="D3" t="n">
-        <v>109.8084807200057</v>
+        <v>97.39428099980483</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.87225929192346</v>
+        <v>29.48188355853172</v>
       </c>
       <c r="C4" t="n">
-        <v>132.0941536064083</v>
+        <v>113.1159887356133</v>
       </c>
       <c r="D4" t="n">
-        <v>151.5062509624805</v>
+        <v>146.3373492996211</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.90113088597411</v>
+        <v>31.3668391506856</v>
       </c>
       <c r="C5" t="n">
-        <v>160.6630117999905</v>
+        <v>128.8298424897877</v>
       </c>
       <c r="D5" t="n">
-        <v>93.53601252211487</v>
+        <v>98.83745012504767</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.89818564286137</v>
+        <v>31.71830482880595</v>
       </c>
       <c r="C6" t="n">
-        <v>140.5185306565502</v>
+        <v>128.8052987971816</v>
       </c>
       <c r="D6" t="n">
-        <v>40.97618567985338</v>
+        <v>43.47178834404877</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.06201433628357</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="C7" t="n">
-        <v>118.1562814492164</v>
+        <v>106.5382791171596</v>
       </c>
       <c r="D7" t="n">
-        <v>30.84160412891355</v>
+        <v>32.09922293805371</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>8.92899537012474</v>
       </c>
       <c r="C8" t="n">
-        <v>80.94509821514951</v>
+        <v>64.58918146239766</v>
       </c>
       <c r="D8" t="n">
-        <v>27.95526587842792</v>
+        <v>28.62285431731576</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>41.3796839862988</v>
+        <v>36.72030938194344</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.70599977254047</v>
       </c>
     </row>
     <row r="17">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>64.99562501195582</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.706899404786709</v>
+        <v>3.434153469455343</v>
       </c>
       <c r="C2" t="n">
-        <v>6.992007149645783</v>
+        <v>4.214642894331557</v>
       </c>
       <c r="D2" t="n">
-        <v>30.77190004191202</v>
+        <v>18.67382308247858</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.38460842035327</v>
+        <v>17.5143790437631</v>
       </c>
       <c r="C3" t="n">
-        <v>26.10467145592269</v>
+        <v>34.69987260660351</v>
       </c>
       <c r="D3" t="n">
-        <v>101.718879637012</v>
+        <v>94.37540680924587</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.87073776487146</v>
+        <v>35.78666731520473</v>
       </c>
       <c r="C4" t="n">
-        <v>116.4342959759675</v>
+        <v>118.8464500853019</v>
       </c>
       <c r="D4" t="n">
-        <v>168.7614486123225</v>
+        <v>159.3297984176234</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.79790850830796</v>
+        <v>37.38004383919731</v>
       </c>
       <c r="C5" t="n">
-        <v>199.4420461177396</v>
+        <v>167.8543137335984</v>
       </c>
       <c r="D5" t="n">
-        <v>121.0740356262379</v>
+        <v>123.8720165833413</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.21140421824511</v>
+        <v>36.70951015719674</v>
       </c>
       <c r="C6" t="n">
-        <v>193.6909680662617</v>
+        <v>165.9978288248677</v>
       </c>
       <c r="D6" t="n">
-        <v>56.59382815901164</v>
+        <v>59.97496725243766</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.38625312059227</v>
+        <v>25.930902112271</v>
       </c>
       <c r="C7" t="n">
-        <v>155.525526063667</v>
+        <v>144.2069567814055</v>
       </c>
       <c r="D7" t="n">
-        <v>34.61446055633404</v>
+        <v>36.23139902522853</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.68556299720053</v>
+        <v>12.76762889372977</v>
       </c>
       <c r="C8" t="n">
-        <v>114.491417269263</v>
+        <v>98.88653751025997</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>65.67499442329461</v>
+        <v>55.35780779936488</v>
       </c>
       <c r="D9" t="n">
-        <v>28.95468504135117</v>
+        <v>29.39843500367073</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>38.86248287260999</v>
+        <v>36.86953503298896</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.7483380970101</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.47158305540374</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>35.50686921949439</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.436116964863836</v>
+        <v>2.039089981720625</v>
       </c>
       <c r="C2" t="n">
-        <v>3.374266859496287</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="D2" t="n">
-        <v>21.46395005794801</v>
+        <v>13.0199380537212</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.69524160552276</v>
+        <v>16.81242943522663</v>
       </c>
       <c r="C3" t="n">
-        <v>28.2252464970958</v>
+        <v>29.06464078422682</v>
       </c>
       <c r="D3" t="n">
-        <v>104.8604722906018</v>
+        <v>92.1566569976481</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.53363844941631</v>
+        <v>39.51338160052563</v>
       </c>
       <c r="C4" t="n">
-        <v>110.2699021410017</v>
+        <v>118.4380430403352</v>
       </c>
       <c r="D4" t="n">
-        <v>181.2051007636508</v>
+        <v>170.1781105495506</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.245986372072</v>
+        <v>39.19627709205391</v>
       </c>
       <c r="C5" t="n">
-        <v>236.7975462643307</v>
+        <v>204.69439633546</v>
       </c>
       <c r="D5" t="n">
-        <v>127.3081335482052</v>
+        <v>130.4742698944011</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.20761609614837</v>
+        <v>30.99377502307181</v>
       </c>
       <c r="C6" t="n">
-        <v>220.780332469544</v>
+        <v>200.7752595001067</v>
       </c>
       <c r="D6" t="n">
-        <v>54.50074205355744</v>
+        <v>58.24414604985053</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.042878103817369</v>
+        <v>8.444012004226815</v>
       </c>
       <c r="C7" t="n">
-        <v>157.741330632152</v>
+        <v>144.0272969515283</v>
       </c>
       <c r="D7" t="n">
-        <v>34.61446055633404</v>
+        <v>35.99185258539232</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>80.94509821514951</v>
+        <v>70.84782307697107</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>31.79389940203295</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>28.06718511671205</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.90016483380309</v>
       </c>
     </row>
     <row r="16">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>30.49799243242716</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.470478134512475</v>
+        <v>3.069925071179776</v>
       </c>
       <c r="C2" t="n">
-        <v>11.61407534123977</v>
+        <v>7.177557465748431</v>
       </c>
       <c r="D2" t="n">
-        <v>21.30490692986003</v>
+        <v>12.0656792851933</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.46390900021901</v>
+        <v>12.080405500757</v>
       </c>
       <c r="C3" t="n">
-        <v>20.83759502263855</v>
+        <v>18.21141991377833</v>
       </c>
       <c r="D3" t="n">
-        <v>98.29258014919066</v>
+        <v>83.1638480267473</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.44055234396211</v>
+        <v>36.39927788265474</v>
       </c>
       <c r="C4" t="n">
-        <v>92.38933120355459</v>
+        <v>96.93285957880883</v>
       </c>
       <c r="D4" t="n">
-        <v>189.7305978273301</v>
+        <v>175.6660802162903</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.20443417332415</v>
+        <v>47.63930734857648</v>
       </c>
       <c r="C5" t="n">
-        <v>221.408651000262</v>
+        <v>212.5729216620407</v>
       </c>
       <c r="D5" t="n">
-        <v>156.4905840569416</v>
+        <v>154.821612959722</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.66675522656639</v>
+        <v>39.28561613314037</v>
       </c>
       <c r="C6" t="n">
-        <v>288.5641209615608</v>
+        <v>256.6043061975101</v>
       </c>
       <c r="D6" t="n">
-        <v>73.05675541152641</v>
+        <v>78.41022564278425</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.08575620763474</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="C7" t="n">
-        <v>226.0120659854752</v>
+        <v>206.0099382591507</v>
       </c>
       <c r="D7" t="n">
-        <v>39.70482240285375</v>
+        <v>42.39971985101125</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>130.0962970282661</v>
+        <v>119.9155733352267</v>
       </c>
       <c r="D8" t="n">
-        <v>32.96217917008666</v>
+        <v>33.71321616383547</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>54.1374954029861</v>
+        <v>49.25624581747095</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
         <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>22.56743447752142</v>
+        <v>23.98900515327081</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>18.00819813899924</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>34.47210713921825</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.330669049881928</v>
+        <v>2.1392282475538</v>
       </c>
       <c r="C2" t="n">
-        <v>6.118251692866123</v>
+        <v>4.929355223023235</v>
       </c>
       <c r="D2" t="n">
-        <v>16.42954783057037</v>
+        <v>9.377654070965532</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.67712817848982</v>
+        <v>11.50117435525138</v>
       </c>
       <c r="C3" t="n">
-        <v>31.51410130632262</v>
+        <v>22.77163800000477</v>
       </c>
       <c r="D3" t="n">
-        <v>94.02197763571704</v>
+        <v>75.89891501532091</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.45407582764332</v>
+        <v>32.21310567174634</v>
       </c>
       <c r="C4" t="n">
-        <v>78.45244079406686</v>
+        <v>77.71220302506477</v>
       </c>
       <c r="D4" t="n">
-        <v>193.9933463591697</v>
+        <v>179.137540098507</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.49958037940395</v>
+        <v>51.8362787842316</v>
       </c>
       <c r="C5" t="n">
-        <v>210.609426253547</v>
+        <v>207.00150344044</v>
       </c>
       <c r="D5" t="n">
-        <v>176.7391304570321</v>
+        <v>170.9222753093697</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.22777513404782</v>
+        <v>45.80638438474769</v>
       </c>
       <c r="C6" t="n">
-        <v>321.6509820900868</v>
+        <v>294.8433792779234</v>
       </c>
       <c r="D6" t="n">
-        <v>87.7083581497058</v>
+        <v>94.91340455117314</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.04961146902685</v>
+        <v>15.9897248590678</v>
       </c>
       <c r="C7" t="n">
-        <v>283.024118666496</v>
+        <v>259.3689077326691</v>
       </c>
       <c r="D7" t="n">
-        <v>44.91495746929157</v>
+        <v>47.54996830749001</v>
       </c>
     </row>
     <row r="8">
@@ -3355,10 +3355,10 @@
         <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>169.6509120323701</v>
+        <v>159.6370854490526</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>34.79804737702819</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>59.79530742256046</v>
+        <v>57.02187015806322</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.21204180858408</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.058144098728814</v>
+        <v>3.07188856658827</v>
       </c>
       <c r="C2" t="n">
-        <v>9.591675070491338</v>
+        <v>6.693555847554753</v>
       </c>
       <c r="D2" t="n">
-        <v>14.35413318379261</v>
+        <v>8.988881980083795</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.51590057081509</v>
+        <v>9.44932165337555</v>
       </c>
       <c r="C3" t="n">
-        <v>28.12707172667112</v>
+        <v>20.91613483897829</v>
       </c>
       <c r="D3" t="n">
-        <v>86.82085822506667</v>
+        <v>67.55896826774425</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.65529304928491</v>
+        <v>27.29945841199106</v>
       </c>
       <c r="C4" t="n">
-        <v>77.43142318165017</v>
+        <v>68.26779011021046</v>
       </c>
       <c r="D4" t="n">
-        <v>194.8739740498791</v>
+        <v>176.3042162240507</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.57321145722246</v>
+        <v>50.46183199828607</v>
       </c>
       <c r="C5" t="n">
-        <v>183.2677526902733</v>
+        <v>179.4880240289231</v>
       </c>
       <c r="D5" t="n">
-        <v>194.165152207413</v>
+        <v>189.0355204527234</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.48565598509524</v>
+        <v>54.82275530055039</v>
       </c>
       <c r="C6" t="n">
-        <v>327.7289821270788</v>
+        <v>309.4949820161028</v>
       </c>
       <c r="D6" t="n">
-        <v>111.7788483624291</v>
+        <v>116.810305346694</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.98511922018283</v>
+        <v>28.68568617038755</v>
       </c>
       <c r="C7" t="n">
-        <v>354.6485041775263</v>
+        <v>328.5379422353781</v>
       </c>
       <c r="D7" t="n">
-        <v>54.49681506274045</v>
+        <v>58.03012505032471</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.094509821514951</v>
+        <v>8.428304040958867</v>
       </c>
       <c r="C8" t="n">
-        <v>242.2511547614217</v>
+        <v>228.7324888739431</v>
       </c>
       <c r="D8" t="n">
-        <v>36.46701847424777</v>
+        <v>37.80219535202343</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>110.6046781081499</v>
+        <v>107.7203033530728</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.61405964570653</v>
       </c>
     </row>
     <row r="10">
@@ -3691,10 +3691,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>42.99073196896783</v>
+        <v>43.56014563743098</v>
       </c>
       <c r="D10" t="n">
         <v>26.47773558353648</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.341108421730148</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C2" t="n">
-        <v>5.692173189223006</v>
+        <v>2.379756435094268</v>
       </c>
       <c r="D2" t="n">
-        <v>8.307549073336508</v>
+        <v>13.88682127657113</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.235439522569987</v>
+        <v>2.219731559302038</v>
       </c>
       <c r="C2" t="n">
-        <v>5.678428721363551</v>
+        <v>3.855323234577225</v>
       </c>
       <c r="D2" t="n">
-        <v>10.6794515267968</v>
+        <v>6.687665361329272</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.32017292477148</v>
+        <v>12.67436286182632</v>
       </c>
       <c r="C3" t="n">
-        <v>35.1023891653447</v>
+        <v>25.56471021858694</v>
       </c>
       <c r="D3" t="n">
-        <v>93.11876974780996</v>
+        <v>71.92774555164256</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.10796085640069</v>
+        <v>38.17329598422873</v>
       </c>
       <c r="C4" t="n">
-        <v>111.2271061526424</v>
+        <v>100.3149804199391</v>
       </c>
       <c r="D4" t="n">
-        <v>196.3416868677281</v>
+        <v>180.9881345210122</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.45305302221007</v>
+        <v>31.80862561759666</v>
       </c>
       <c r="C5" t="n">
-        <v>276.9019399828129</v>
+        <v>265.2436859948821</v>
       </c>
       <c r="D5" t="n">
-        <v>173.842974729504</v>
+        <v>170.9959063871882</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.99249017573129</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="C6" t="n">
-        <v>288.2018560586937</v>
+        <v>273.9930215351296</v>
       </c>
       <c r="D6" t="n">
-        <v>85.25300714138454</v>
+        <v>90.48572240502003</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.329908286355933</v>
+        <v>5.569454726192155</v>
       </c>
       <c r="C7" t="n">
-        <v>170.3175187235536</v>
+        <v>160.8554343500229</v>
       </c>
       <c r="D7" t="n">
-        <v>32.03933632809466</v>
+        <v>33.95570784678443</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>81.52923809917637</v>
+        <v>79.35957567279091</v>
       </c>
       <c r="D8" t="n">
-        <v>24.20008090968387</v>
+        <v>24.70077223884975</v>
       </c>
     </row>
     <row r="9">
@@ -4299,10 +4299,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.17030968338697</v>
       </c>
       <c r="D9" t="n">
         <v>20.1906232855399</v>
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.4988920646734</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.10418842983717</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.251589454194441</v>
+        <v>5.789366211943441</v>
       </c>
       <c r="C2" t="n">
-        <v>6.659194677906115</v>
+        <v>5.475206946584461</v>
       </c>
       <c r="D2" t="n">
-        <v>27.96017461694916</v>
+        <v>13.93689040948772</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.46957850226624</v>
+        <v>10.88758204009713</v>
       </c>
       <c r="C3" t="n">
-        <v>14.3433339590459</v>
+        <v>5.993569734426778</v>
       </c>
       <c r="D3" t="n">
-        <v>10.11200135374215</v>
+        <v>14.79984664152067</v>
       </c>
     </row>
     <row r="4">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39851021320011</v>
+        <v>13.39832970268153</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14514170440059</v>
+        <v>70.14419667874446</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576295319200013</v>
+        <v>1.576274082668415</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.944081438586937</v>
+        <v>4.233296100712247</v>
       </c>
       <c r="C2" t="n">
-        <v>5.060909415392308</v>
+        <v>4.82921695719006</v>
       </c>
       <c r="D2" t="n">
-        <v>29.81273253486289</v>
+        <v>30.51860913421634</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.45256999612455</v>
+        <v>16.35100801423063</v>
       </c>
       <c r="C3" t="n">
-        <v>21.61808444751476</v>
+        <v>15.76195939168254</v>
       </c>
       <c r="D3" t="n">
-        <v>31.1508546557513</v>
+        <v>22.92871763268426</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>15.64709491028566</v>
+        <v>12.72443199474291</v>
       </c>
       <c r="C4" t="n">
-        <v>22.39857387239098</v>
+        <v>9.827294519510573</v>
       </c>
       <c r="D4" t="n">
-        <v>20.36930136771282</v>
+        <v>22.83250635766807</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>16.42267559664065</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3346624606237</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43941654534036</v>
+        <v>15.44376274800173</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13569230558306</v>
+        <v>86.15993954148335</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25040348322955</v>
+        <v>3.251318473263523</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.39528447191297</v>
+        <v>4.286310476741575</v>
       </c>
       <c r="C2" t="n">
-        <v>8.360563449365838</v>
+        <v>7.478954010952201</v>
       </c>
       <c r="D2" t="n">
-        <v>23.54427344324701</v>
+        <v>34.67729240940584</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.44351328260808</v>
+        <v>15.39871274111122</v>
       </c>
       <c r="C3" t="n">
-        <v>20.65597169735289</v>
+        <v>17.59782759862408</v>
       </c>
       <c r="D3" t="n">
-        <v>47.77184328864979</v>
+        <v>42.02371048028472</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.43457974227862</v>
+        <v>23.38130332434203</v>
       </c>
       <c r="C4" t="n">
-        <v>40.5343992129423</v>
+        <v>27.26117025152543</v>
       </c>
       <c r="D4" t="n">
-        <v>31.38352886165779</v>
+        <v>29.18834099496192</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.54811831860599</v>
+        <v>11.53553552490002</v>
       </c>
       <c r="C5" t="n">
-        <v>25.9181393921158</v>
+        <v>12.61545799957152</v>
       </c>
       <c r="D5" t="n">
-        <v>29.99239236474006</v>
+        <v>30.63052837250049</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.876741757621407</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.34724525432967</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.19419042345839</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.66867766424586</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
         <v>41.26874649571891</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5336,7 +5336,7 @@
         <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72933202299591</v>
+        <v>16.74035339319731</v>
       </c>
       <c r="C21" t="n">
-        <v>102.048925340275</v>
+        <v>102.1161556985036</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182333005748977</v>
+        <v>5.022106017959192</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.075635630956009</v>
+        <v>4.516039439535327</v>
       </c>
       <c r="C2" t="n">
-        <v>6.806456833543137</v>
+        <v>9.355073873767855</v>
       </c>
       <c r="D2" t="n">
-        <v>26.79778533512093</v>
+        <v>27.75400759905733</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.02841393016093</v>
+        <v>15.01092239793373</v>
       </c>
       <c r="C3" t="n">
-        <v>27.44966581074082</v>
+        <v>24.18535469412017</v>
       </c>
       <c r="D3" t="n">
-        <v>55.03677630007619</v>
+        <v>59.02758071783948</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.53592073999429</v>
+        <v>26.78894960578271</v>
       </c>
       <c r="C4" t="n">
-        <v>46.76260664868407</v>
+        <v>36.37375244234432</v>
       </c>
       <c r="D4" t="n">
-        <v>47.34969177582366</v>
+        <v>42.6147225982413</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.31146036862028</v>
+        <v>23.58648859452962</v>
       </c>
       <c r="C5" t="n">
-        <v>52.35169632896118</v>
+        <v>33.35487825178539</v>
       </c>
       <c r="D5" t="n">
-        <v>34.01755795215198</v>
+        <v>34.3366259560322</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.99499345048753</v>
+        <v>10.74719211838983</v>
       </c>
       <c r="C6" t="n">
-        <v>27.08936440328224</v>
+        <v>16.38242394076653</v>
       </c>
       <c r="D6" t="n">
-        <v>38.03781480104267</v>
+        <v>38.44033135978387</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
-        <v>39.64493579289469</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.16874709860598</v>
       </c>
       <c r="D9" t="n">
-        <v>42.26718391093791</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5588,10 +5588,10 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>46.86470840992573</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.77765165941727</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05093054232188</v>
+        <v>18.07029499594481</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7608325856237</v>
+        <v>117.8871625925923</v>
       </c>
       <c r="D21" t="n">
-        <v>6.016976847440628</v>
+        <v>6.883921903217068</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.849252821902496</v>
+        <v>6.077018289287756</v>
       </c>
       <c r="C2" t="n">
-        <v>10.93470592990098</v>
+        <v>8.259443435828414</v>
       </c>
       <c r="D2" t="n">
-        <v>28.75440850968483</v>
+        <v>33.68278198500381</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.32999040181394</v>
+        <v>13.66101930459437</v>
       </c>
       <c r="C3" t="n">
-        <v>25.2407334761855</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D3" t="n">
-        <v>59.42518853805944</v>
+        <v>63.02820261264523</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.5171854181556</v>
+        <v>20.56074217004095</v>
       </c>
       <c r="C4" t="n">
-        <v>49.41725244096745</v>
+        <v>42.02763747110171</v>
       </c>
       <c r="D4" t="n">
-        <v>55.28810371236337</v>
+        <v>53.37369568908209</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.03456645829367</v>
+        <v>19.58586669972387</v>
       </c>
       <c r="C5" t="n">
-        <v>52.44987109938586</v>
+        <v>38.55814108429348</v>
       </c>
       <c r="D5" t="n">
-        <v>34.41025703385071</v>
+        <v>34.01755795215198</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.41009280293469</v>
+        <v>11.79373517111693</v>
       </c>
       <c r="C6" t="n">
-        <v>37.59504658642736</v>
+        <v>23.90948358922682</v>
       </c>
       <c r="D6" t="n">
-        <v>31.23528495831652</v>
+        <v>31.27553661419064</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.749114556069321</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>19.52303484665207</v>
+        <v>14.55244622005047</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>31.20092378866788</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>22.18749811597791</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5874,7 +5874,7 @@
         <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.053193947116112</v>
+        <v>7.064815248714824</v>
       </c>
       <c r="C21" t="n">
-        <v>67.00534249760307</v>
+        <v>66.23264295670147</v>
       </c>
       <c r="D21" t="n">
-        <v>4.40824621694757</v>
+        <v>5.298611436536118</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.3715426005618</v>
+        <v>4.817435984739099</v>
       </c>
       <c r="C2" t="n">
-        <v>11.3902368646715</v>
+        <v>5.513495107050087</v>
       </c>
       <c r="D2" t="n">
-        <v>31.15870863738527</v>
+        <v>28.57573042751191</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.43231314723387</v>
+        <v>18.34886459237289</v>
       </c>
       <c r="C3" t="n">
-        <v>36.51610585946011</v>
+        <v>31.31284302695202</v>
       </c>
       <c r="D3" t="n">
-        <v>69.21812188792136</v>
+        <v>76.83157533435538</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.88654353913065</v>
+        <v>24.61928717939726</v>
       </c>
       <c r="C4" t="n">
-        <v>58.18524118759571</v>
+        <v>62.33312523803848</v>
       </c>
       <c r="D4" t="n">
-        <v>73.06657288856887</v>
+        <v>75.08308267309181</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.2749557771139</v>
+        <v>26.21266370338984</v>
       </c>
       <c r="C5" t="n">
-        <v>76.28179661997717</v>
+        <v>62.90548414961439</v>
       </c>
       <c r="D5" t="n">
-        <v>47.86020058203201</v>
+        <v>46.80482179996669</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.64030479181395</v>
+        <v>20.48809283992669</v>
       </c>
       <c r="C6" t="n">
-        <v>64.52340436621313</v>
+        <v>46.249152599363</v>
       </c>
       <c r="D6" t="n">
-        <v>35.62271544859552</v>
+        <v>35.22019888985433</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.15698182168825</v>
+        <v>10.42027013287564</v>
       </c>
       <c r="C7" t="n">
-        <v>39.82459562277186</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D7" t="n">
-        <v>33.0574086973986</v>
+        <v>33.83593462686632</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>23.11524969649115</v>
+        <v>19.44351328260808</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>32.46148784092078</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6238,7 +6238,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.273213471465229</v>
+        <v>7.289035031616386</v>
       </c>
       <c r="C21" t="n">
-        <v>76.36874145038492</v>
+        <v>75.62373845302001</v>
       </c>
       <c r="D21" t="n">
-        <v>5.454910103598922</v>
+        <v>6.377905652664338</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.167339078078462</v>
+        <v>3.683517386334032</v>
       </c>
       <c r="C2" t="n">
-        <v>9.19701249338412</v>
+        <v>5.069745144730529</v>
       </c>
       <c r="D2" t="n">
-        <v>40.40873550679871</v>
+        <v>22.34065075784042</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.39580855572748</v>
+        <v>17.60764507566654</v>
       </c>
       <c r="C3" t="n">
-        <v>41.14504628498383</v>
+        <v>25.33399950808894</v>
       </c>
       <c r="D3" t="n">
-        <v>78.08330365727006</v>
+        <v>81.86303231862028</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.18758023143592</v>
+        <v>30.82196917482861</v>
       </c>
       <c r="C4" t="n">
-        <v>77.43142318165017</v>
+        <v>71.24150390637404</v>
       </c>
       <c r="D4" t="n">
-        <v>91.36831359113789</v>
+        <v>96.72865605632549</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.87091769132071</v>
+        <v>32.42221793275092</v>
       </c>
       <c r="C5" t="n">
-        <v>93.09422605520381</v>
+        <v>93.31511928865933</v>
       </c>
       <c r="D5" t="n">
-        <v>63.29818323131311</v>
+        <v>62.70913460876503</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.26045054572845</v>
+        <v>28.6591789823729</v>
       </c>
       <c r="C6" t="n">
-        <v>95.75868932452966</v>
+        <v>76.27688788145595</v>
       </c>
       <c r="D6" t="n">
-        <v>42.18373535607696</v>
+        <v>42.2642386678252</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.97838585497334</v>
+        <v>18.1456428175938</v>
       </c>
       <c r="C7" t="n">
-        <v>68.92948806287281</v>
+        <v>48.80758711663017</v>
       </c>
       <c r="D7" t="n">
-        <v>36.23139902522853</v>
+        <v>36.4110588551057</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
-        <v>39.22082078466007</v>
+        <v>28.12216298814988</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>34.71459882216722</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>26.5140602485936</v>
+        <v>24.51718541815559</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -6493,7 +6493,7 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
         <v>34.30717352490479</v>
@@ -6510,7 +6510,7 @@
         <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.479101816813724</v>
+        <v>7.500820778200025</v>
       </c>
       <c r="C21" t="n">
-        <v>85.07478316625611</v>
+        <v>85.32183635202529</v>
       </c>
       <c r="D21" t="n">
-        <v>6.544214089712009</v>
+        <v>7.500820778200025</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_73_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_73_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497646523778</v>
+        <v>10.84497649115302</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907240542412</v>
+        <v>37.7890724957252</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.285729639664827</v>
+        <v>4.862596379134452</v>
       </c>
       <c r="C2" t="n">
-        <v>4.2784564951076</v>
+        <v>10.10414737210817</v>
       </c>
       <c r="D2" t="n">
-        <v>21.34515858573415</v>
+        <v>18.05924901962008</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.87838645786041</v>
+        <v>17.64691498383642</v>
       </c>
       <c r="C3" t="n">
-        <v>22.09423208407447</v>
+        <v>31.43556148998287</v>
       </c>
       <c r="D3" t="n">
-        <v>80.63093894979055</v>
+        <v>62.17899084847173</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.64703815702343</v>
+        <v>36.36098972218912</v>
       </c>
       <c r="C4" t="n">
-        <v>66.91494177375834</v>
+        <v>84.54025830810133</v>
       </c>
       <c r="D4" t="n">
-        <v>114.9665831581185</v>
+        <v>84.75722455073988</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.29445186247859</v>
+        <v>42.90237467558562</v>
       </c>
       <c r="C5" t="n">
-        <v>112.7046364475339</v>
+        <v>117.048870038826</v>
       </c>
       <c r="D5" t="n">
-        <v>81.48505945248527</v>
+        <v>63.93631923907354</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.46800022195202</v>
+        <v>37.0315234041897</v>
       </c>
       <c r="C6" t="n">
-        <v>113.751179500261</v>
+        <v>132.8707160404676</v>
       </c>
       <c r="D6" t="n">
-        <v>52.1258943569844</v>
+        <v>46.00764266411829</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.58965482182061</v>
+        <v>26.88908787161589</v>
       </c>
       <c r="C7" t="n">
-        <v>80.42771717501144</v>
+        <v>136.0623778269739</v>
       </c>
       <c r="D7" t="n">
-        <v>40.42346172236242</v>
+        <v>38.68675003354981</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.26970288122739</v>
+        <v>14.85384276525424</v>
       </c>
       <c r="C8" t="n">
-        <v>46.56429361242621</v>
+        <v>99.88792016859172</v>
       </c>
       <c r="D8" t="n">
-        <v>36.46701847424777</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -881,10 +881,10 @@
         <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>30.39687241888974</v>
+        <v>52.02968308196819</v>
       </c>
       <c r="D9" t="n">
-        <v>34.50155957034565</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>28.75539025738908</v>
+        <v>32.17187226816798</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1010,7 +1010,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.699183547094685</v>
+        <v>7.662904218537534</v>
       </c>
       <c r="C21" t="n">
-        <v>94.31499845190987</v>
+        <v>92.9127136497676</v>
       </c>
       <c r="D21" t="n">
-        <v>8.66158149048152</v>
+        <v>7.662904218537534</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.255295460833175</v>
+        <v>5.614615120587509</v>
       </c>
       <c r="C2" t="n">
-        <v>14.61625982082651</v>
+        <v>11.52866329097029</v>
       </c>
       <c r="D2" t="n">
-        <v>30.83964063350506</v>
+        <v>22.24345773511998</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.22828955119978</v>
+        <v>16.99405276051229</v>
       </c>
       <c r="C3" t="n">
-        <v>19.11953654020664</v>
+        <v>35.19074645872691</v>
       </c>
       <c r="D3" t="n">
-        <v>78.76070957320036</v>
+        <v>61.82065293642165</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.24764676784423</v>
+        <v>34.52315801983909</v>
       </c>
       <c r="C4" t="n">
-        <v>60.87817514034472</v>
+        <v>81.45168003054087</v>
       </c>
       <c r="D4" t="n">
-        <v>125.8148952900457</v>
+        <v>94.72490899195775</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.71231653158924</v>
+        <v>47.81111319681967</v>
       </c>
       <c r="C5" t="n">
-        <v>116.7788894201581</v>
+        <v>134.0085616296896</v>
       </c>
       <c r="D5" t="n">
-        <v>101.7826932377881</v>
+        <v>76.57632093125122</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.67933802027235</v>
+        <v>46.249152599363</v>
       </c>
       <c r="C6" t="n">
-        <v>145.3487293614446</v>
+        <v>157.665736058925</v>
       </c>
       <c r="D6" t="n">
-        <v>63.3963580017378</v>
+        <v>54.42023874180921</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.49468733641593</v>
+        <v>34.97378021608837</v>
       </c>
       <c r="C7" t="n">
-        <v>119.5935600882337</v>
+        <v>161.2147540097772</v>
       </c>
       <c r="D7" t="n">
-        <v>45.8132566186774</v>
+        <v>42.27994663109313</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.02903582496668</v>
+        <v>21.11248437982766</v>
       </c>
       <c r="C8" t="n">
-        <v>75.35404503946393</v>
+        <v>137.6066669657542</v>
       </c>
       <c r="D8" t="n">
-        <v>38.63668090063322</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -1192,10 +1192,10 @@
         <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>43.26562132615692</v>
+        <v>83.86874287839649</v>
       </c>
       <c r="D9" t="n">
-        <v>36.16562192904399</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>45.69544689416779</v>
       </c>
       <c r="D10" t="n">
         <v>35.3036474447153</v>
@@ -1220,10 +1220,10 @@
         <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>31.8076438698924</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.02617269731195</v>
+        <v>30.15830772675777</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>27.3171298706675</v>
       </c>
       <c r="D13" t="n">
         <v>32.780555844801</v>
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.88327797516992</v>
+        <v>7.837362693330741</v>
       </c>
       <c r="C21" t="n">
-        <v>103.4680234241052</v>
+        <v>100.9060446766333</v>
       </c>
       <c r="D21" t="n">
-        <v>9.854097468962401</v>
+        <v>8.817033029997084</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.211918635397069</v>
+        <v>6.874197425136166</v>
       </c>
       <c r="C2" t="n">
-        <v>16.66025854106837</v>
+        <v>15.23279737909351</v>
       </c>
       <c r="D2" t="n">
-        <v>41.75863860013808</v>
+        <v>20.14840813425729</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.63080610994097</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="C3" t="n">
-        <v>36.80081269369169</v>
+        <v>39.20609456909637</v>
       </c>
       <c r="D3" t="n">
-        <v>83.24729658160828</v>
+        <v>63.7890570834365</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.24764676784423</v>
+        <v>32.7491399182651</v>
       </c>
       <c r="C4" t="n">
-        <v>54.08840801777377</v>
+        <v>83.21293541195965</v>
       </c>
       <c r="D4" t="n">
-        <v>134.1106633909313</v>
+        <v>100.429844901336</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.17864669110647</v>
+        <v>49.50462798664542</v>
       </c>
       <c r="C5" t="n">
-        <v>113.3427724552943</v>
+        <v>140.5617275555371</v>
       </c>
       <c r="D5" t="n">
-        <v>117.8833555874358</v>
+        <v>89.43721585688444</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.67683474551611</v>
+        <v>53.25294072145974</v>
       </c>
       <c r="C6" t="n">
-        <v>163.5022261606723</v>
+        <v>179.2003719515788</v>
       </c>
       <c r="D6" t="n">
-        <v>77.4441859018054</v>
+        <v>62.71207985187777</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.51949307092936</v>
+        <v>42.93869934064274</v>
       </c>
       <c r="C7" t="n">
-        <v>158.1006502919063</v>
+        <v>188.2835017112703</v>
       </c>
       <c r="D7" t="n">
-        <v>51.50248456478767</v>
+        <v>47.13076203777662</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.28906009787184</v>
+        <v>27.78836876870596</v>
       </c>
       <c r="C8" t="n">
-        <v>111.9879606234336</v>
+        <v>170.7357432455628</v>
       </c>
       <c r="D8" t="n">
-        <v>41.64082887562846</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.08749871886498</v>
+        <v>14.97656122828509</v>
       </c>
       <c r="C9" t="n">
-        <v>64.5656195174957</v>
+        <v>118.9249899016416</v>
       </c>
       <c r="D9" t="n">
-        <v>37.27499683484289</v>
+        <v>37.05312185368311</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.114144775599888</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>40.85543071223102</v>
+        <v>67.04845946153593</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>35.00617789032851</v>
+        <v>41.04785326226338</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>30.95941385342317</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1632,7 +1632,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.051585685354732</v>
+        <v>7.995446662313685</v>
       </c>
       <c r="C21" t="n">
-        <v>111.7157513842969</v>
+        <v>107.9385299412347</v>
       </c>
       <c r="D21" t="n">
-        <v>11.07093031736276</v>
+        <v>9.994308327892107</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.48542533425443</v>
+        <v>6.308710747490003</v>
       </c>
       <c r="C2" t="n">
-        <v>11.32838675930394</v>
+        <v>10.6018934581613</v>
       </c>
       <c r="D2" t="n">
-        <v>34.04602863557513</v>
+        <v>16.73094437577414</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.53816197284327</v>
+        <v>21.56899706230243</v>
       </c>
       <c r="C3" t="n">
-        <v>53.711416899343</v>
+        <v>59.07666810305182</v>
       </c>
       <c r="D3" t="n">
-        <v>92.06829970426588</v>
+        <v>70.03788122096745</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.22440361811179</v>
+        <v>23.7769476491535</v>
       </c>
       <c r="C4" t="n">
-        <v>86.68439529417637</v>
+        <v>114.9027695573424</v>
       </c>
       <c r="D4" t="n">
-        <v>131.2007631955437</v>
+        <v>97.69862278812133</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.54431450097602</v>
+        <v>29.99239236474006</v>
       </c>
       <c r="C5" t="n">
-        <v>97.68389657255766</v>
+        <v>107.0595871481147</v>
       </c>
       <c r="D5" t="n">
-        <v>77.95076771719675</v>
+        <v>61.50649367106269</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.40508625342222</v>
+        <v>26.64659618866693</v>
       </c>
       <c r="C6" t="n">
-        <v>104.1310337463464</v>
+        <v>124.0153517481614</v>
       </c>
       <c r="D6" t="n">
-        <v>33.89189424600839</v>
+        <v>31.03402667894593</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.74450891718435</v>
+        <v>18.38518925743002</v>
       </c>
       <c r="C7" t="n">
-        <v>78.75089209615788</v>
+        <v>120.0726529679061</v>
       </c>
       <c r="D7" t="n">
-        <v>29.2845522699781</v>
+        <v>28.14670668075605</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>47.56567627075796</v>
+        <v>87.62098260402782</v>
       </c>
       <c r="D8" t="n">
-        <v>27.45457454926205</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>31.17343485294896</v>
+        <v>51.14218315732908</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>27.47420950334699</v>
+        <v>32.17187226816798</v>
       </c>
       <c r="D10" t="n">
-        <v>29.04009709162065</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1929,7 +1929,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.861213720802705</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C2" t="n">
-        <v>5.408448102695679</v>
+        <v>5.210135066437823</v>
       </c>
       <c r="D2" t="n">
-        <v>23.29687302177681</v>
+        <v>12.76566539832127</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.00587479069226</v>
+        <v>22.15313694632928</v>
       </c>
       <c r="C3" t="n">
-        <v>49.85805716017427</v>
+        <v>51.2619563772472</v>
       </c>
       <c r="D3" t="n">
-        <v>97.39428099980483</v>
+        <v>68.52598975642736</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.48188355853172</v>
+        <v>31.15379989886403</v>
       </c>
       <c r="C4" t="n">
-        <v>113.1159887356133</v>
+        <v>133.2810865808427</v>
       </c>
       <c r="D4" t="n">
-        <v>146.3373492996211</v>
+        <v>107.8194598712017</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.3668391506856</v>
+        <v>33.45305302221007</v>
       </c>
       <c r="C5" t="n">
-        <v>128.8298424897877</v>
+        <v>155.8769917417874</v>
       </c>
       <c r="D5" t="n">
-        <v>98.83745012504767</v>
+        <v>77.16536955379931</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.71830482880595</v>
+        <v>31.87931145230244</v>
       </c>
       <c r="C6" t="n">
-        <v>128.8052987971816</v>
+        <v>147.6833254021435</v>
       </c>
       <c r="D6" t="n">
-        <v>43.47178834404877</v>
+        <v>37.59504658642736</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.66654993792135</v>
+        <v>17.24734366820796</v>
       </c>
       <c r="C7" t="n">
-        <v>106.5382791171596</v>
+        <v>147.6204935490717</v>
       </c>
       <c r="D7" t="n">
-        <v>32.09922293805371</v>
+        <v>30.60205768907732</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.92899537012474</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
-        <v>64.58918146239766</v>
+        <v>112.4886519525995</v>
       </c>
       <c r="D8" t="n">
-        <v>28.62285431731576</v>
+        <v>28.03871443328891</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>4.659374604355361</v>
       </c>
       <c r="C9" t="n">
-        <v>36.72030938194344</v>
+        <v>56.57812019574367</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>28.17812260729194</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>33.88011327355743</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2150,10 +2150,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
         <v>29.49759152179966</v>
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
         <v>28.42257778564941</v>
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2226,7 +2226,7 @@
         <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.434153469455343</v>
+        <v>3.77972866135022</v>
       </c>
       <c r="C2" t="n">
-        <v>4.214642894331557</v>
+        <v>14.25497666566369</v>
       </c>
       <c r="D2" t="n">
-        <v>18.67382308247858</v>
+        <v>19.19120412261665</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.5143790437631</v>
+        <v>17.87762569433442</v>
       </c>
       <c r="C3" t="n">
-        <v>34.69987260660351</v>
+        <v>35.23001636689679</v>
       </c>
       <c r="D3" t="n">
-        <v>94.37540680924587</v>
+        <v>63.27854827722817</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.78666731520473</v>
+        <v>36.08020987877453</v>
       </c>
       <c r="C4" t="n">
-        <v>118.8464500853019</v>
+        <v>130.4988135870073</v>
       </c>
       <c r="D4" t="n">
-        <v>159.3297984176234</v>
+        <v>116.0131262108456</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.38004383919731</v>
+        <v>39.46625771072178</v>
       </c>
       <c r="C5" t="n">
-        <v>167.8543137335984</v>
+        <v>200.3992501293802</v>
       </c>
       <c r="D5" t="n">
-        <v>123.8720165833413</v>
+        <v>94.81228453763572</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.70951015719674</v>
+        <v>37.75605320992383</v>
       </c>
       <c r="C6" t="n">
-        <v>165.9978288248677</v>
+        <v>192.9261866046535</v>
       </c>
       <c r="D6" t="n">
-        <v>59.97496725243766</v>
+        <v>49.87180162803373</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.930902112271</v>
+        <v>25.45180923259856</v>
       </c>
       <c r="C7" t="n">
-        <v>144.2069567814055</v>
+        <v>179.360396827371</v>
       </c>
       <c r="D7" t="n">
-        <v>36.23139902522853</v>
+        <v>33.71616140694821</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.76762889372977</v>
+        <v>12.35038611942487</v>
       </c>
       <c r="C8" t="n">
-        <v>98.88653751025997</v>
+        <v>150.04050164004</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>29.54078842078653</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>55.35780779936488</v>
+        <v>90.74686729434964</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.17656002251095</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>36.86953503298896</v>
+        <v>47.40368789955724</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2461,10 +2461,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
         <v>30.03068052520567</v>
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>14.46605242207675</v>
+      </c>
+      <c r="D16" t="n">
         <v>14.87936820556466</v>
-      </c>
-      <c r="D16" t="n">
-        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.039089981720625</v>
+        <v>2.295326132529043</v>
       </c>
       <c r="C2" t="n">
-        <v>1.992947839621025</v>
+        <v>6.87321567743192</v>
       </c>
       <c r="D2" t="n">
-        <v>13.0199380537212</v>
+        <v>13.38416645199677</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.81242943522663</v>
+        <v>17.48492661263569</v>
       </c>
       <c r="C3" t="n">
-        <v>29.06464078422682</v>
+        <v>45.46473618366979</v>
       </c>
       <c r="D3" t="n">
-        <v>92.1566569976481</v>
+        <v>65.25676990128549</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.51338160052563</v>
+        <v>39.65377152223292</v>
       </c>
       <c r="C4" t="n">
-        <v>118.4380430403352</v>
+        <v>129.2353042916416</v>
       </c>
       <c r="D4" t="n">
-        <v>170.1781105495506</v>
+        <v>122.7135542923301</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.19627709205391</v>
+        <v>40.54618018539328</v>
       </c>
       <c r="C5" t="n">
-        <v>204.69439633546</v>
+        <v>240.9208866221673</v>
       </c>
       <c r="D5" t="n">
-        <v>130.4742698944011</v>
+        <v>99.79465413668829</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.99377502307181</v>
+        <v>30.79251674370121</v>
       </c>
       <c r="C6" t="n">
-        <v>200.7752595001067</v>
+        <v>228.5891537091231</v>
       </c>
       <c r="D6" t="n">
-        <v>58.24414604985053</v>
+        <v>49.02651685467723</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.444012004226815</v>
+        <v>8.144578954431539</v>
       </c>
       <c r="C7" t="n">
-        <v>144.0272969515283</v>
+        <v>189.8405535702057</v>
       </c>
       <c r="D7" t="n">
-        <v>35.99185258539232</v>
+        <v>33.89582123682538</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>70.84782307697107</v>
+        <v>110.9865779651019</v>
       </c>
       <c r="D8" t="n">
-        <v>31.79389940203295</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>28.06718511671205</v>
+        <v>36.16562192904399</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -2758,10 +2758,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
         <v>23.48831382410494</v>
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>19.72429312602266</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>12.18348900970292</v>
+      </c>
+      <c r="D15" t="n">
         <v>12.541826921753</v>
-      </c>
-      <c r="D15" t="n">
-        <v>12.90016483380309</v>
       </c>
     </row>
     <row r="16">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.069925071179776</v>
+        <v>2.493639168786898</v>
       </c>
       <c r="C2" t="n">
-        <v>7.177557465748431</v>
+        <v>9.874418409314419</v>
       </c>
       <c r="D2" t="n">
-        <v>12.0656792851933</v>
+        <v>12.04113559258713</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.080405500757</v>
+        <v>12.90507357232432</v>
       </c>
       <c r="C3" t="n">
-        <v>18.21141991377833</v>
+        <v>36.16267668593126</v>
       </c>
       <c r="D3" t="n">
-        <v>83.1638480267473</v>
+        <v>61.18742566718246</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.39927788265474</v>
+        <v>37.01188845010475</v>
       </c>
       <c r="C4" t="n">
-        <v>96.93285957880883</v>
+        <v>122.7007915721749</v>
       </c>
       <c r="D4" t="n">
-        <v>175.6660802162903</v>
+        <v>126.1850141745468</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.63930734857648</v>
+        <v>48.30198704894308</v>
       </c>
       <c r="C5" t="n">
-        <v>212.5729216620407</v>
+        <v>241.4853915521092</v>
       </c>
       <c r="D5" t="n">
-        <v>154.821612959722</v>
+        <v>116.3616466458532</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.28561613314037</v>
+        <v>39.48687441251096</v>
       </c>
       <c r="C6" t="n">
-        <v>256.6043061975101</v>
+        <v>295.9301739865246</v>
       </c>
       <c r="D6" t="n">
-        <v>78.41022564278425</v>
+        <v>64.24164277509429</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.66654993792135</v>
+        <v>17.00779722837174</v>
       </c>
       <c r="C7" t="n">
-        <v>206.0099382591507</v>
+        <v>250.8650091184832</v>
       </c>
       <c r="D7" t="n">
-        <v>42.39971985101125</v>
+        <v>38.08788393395925</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>119.9155733352267</v>
+        <v>165.7288299539041</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>32.87873061522568</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>49.25624581747095</v>
+        <v>70.66718149938963</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
+        <v>23.27821981539612</v>
+      </c>
+      <c r="D11" t="n">
         <v>23.98900515327081</v>
-      </c>
-      <c r="D11" t="n">
-        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
         <v>21.47965802121596</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>15.08946221427348</v>
+      </c>
+      <c r="D13" t="n">
         <v>15.60978849752428</v>
-      </c>
-      <c r="D13" t="n">
-        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.1392282475538</v>
+        <v>1.68664255589602</v>
       </c>
       <c r="C2" t="n">
-        <v>4.929355223023235</v>
+        <v>6.365652114336318</v>
       </c>
       <c r="D2" t="n">
-        <v>9.377654070965532</v>
+        <v>9.262789589568657</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.50117435525138</v>
+        <v>11.20665004397734</v>
       </c>
       <c r="C3" t="n">
-        <v>22.77163800000477</v>
+        <v>37.8120128290659</v>
       </c>
       <c r="D3" t="n">
-        <v>75.89891501532091</v>
+        <v>57.84457473422207</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.21310567174634</v>
+        <v>32.91505528028281</v>
       </c>
       <c r="C4" t="n">
-        <v>77.71220302506477</v>
+        <v>111.4823605557466</v>
       </c>
       <c r="D4" t="n">
-        <v>179.137540098507</v>
+        <v>127.665489712551</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.8362787842316</v>
+        <v>52.44987109938586</v>
       </c>
       <c r="C5" t="n">
-        <v>207.00150344044</v>
+        <v>243.8170423496954</v>
       </c>
       <c r="D5" t="n">
-        <v>170.9222753093697</v>
+        <v>128.3880560228766</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.80638438474769</v>
+        <v>45.56487444950297</v>
       </c>
       <c r="C6" t="n">
-        <v>294.8433792779234</v>
+        <v>337.3491278809933</v>
       </c>
       <c r="D6" t="n">
-        <v>94.91340455117314</v>
+        <v>74.42531171124647</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.9897248590678</v>
+        <v>15.09142570968197</v>
       </c>
       <c r="C7" t="n">
-        <v>259.3689077326691</v>
+        <v>310.6318458576205</v>
       </c>
       <c r="D7" t="n">
-        <v>47.54996830749001</v>
+        <v>42.27994663109313</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>159.6370854490526</v>
+        <v>208.6213871524472</v>
       </c>
       <c r="D8" t="n">
-        <v>34.79804737702819</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>57.02187015806322</v>
+        <v>77.21249344360311</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.48126166372597</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.07188856658827</v>
+        <v>2.75478405811655</v>
       </c>
       <c r="C2" t="n">
-        <v>6.693555847554753</v>
+        <v>7.071528713689775</v>
       </c>
       <c r="D2" t="n">
-        <v>8.988881980083795</v>
+        <v>9.140071126537803</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.44932165337555</v>
+        <v>8.659014751456867</v>
       </c>
       <c r="C3" t="n">
-        <v>20.91613483897829</v>
+        <v>31.74481201682061</v>
       </c>
       <c r="D3" t="n">
-        <v>67.55896826774425</v>
+        <v>52.94074495150925</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.29945841199106</v>
+        <v>27.50366193447439</v>
       </c>
       <c r="C4" t="n">
-        <v>68.26779011021046</v>
+        <v>103.8502539029318</v>
       </c>
       <c r="D4" t="n">
-        <v>176.3042162240507</v>
+        <v>126.8359129024624</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.46183199828607</v>
+        <v>51.66447293598841</v>
       </c>
       <c r="C5" t="n">
-        <v>179.4880240289231</v>
+        <v>227.4218556887737</v>
       </c>
       <c r="D5" t="n">
-        <v>189.0355204527234</v>
+        <v>137.8619213688584</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.82275530055039</v>
+        <v>54.17872880656449</v>
       </c>
       <c r="C6" t="n">
-        <v>309.4949820161028</v>
+        <v>357.4347041621788</v>
       </c>
       <c r="D6" t="n">
-        <v>116.810305346694</v>
+        <v>90.44547074914593</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.68568617038755</v>
+        <v>27.008861091534</v>
       </c>
       <c r="C7" t="n">
-        <v>328.5379422353781</v>
+        <v>377.9443954515988</v>
       </c>
       <c r="D7" t="n">
-        <v>58.03012505032471</v>
+        <v>49.88554609589318</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>228.7324888739431</v>
+        <v>285.2271605148258</v>
       </c>
       <c r="D8" t="n">
-        <v>37.80219535202343</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>107.7203033530728</v>
+        <v>138.6718632248619</v>
       </c>
       <c r="D9" t="n">
-        <v>33.61405964570653</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>43.56014563743098</v>
+        <v>51.24723016168351</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.76244241776806</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.8983245115816</v>
+        <v>27.36523550817559</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.09302935219197</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.124723016168351</v>
+        <v>5.871833019100173</v>
       </c>
       <c r="C2" t="n">
-        <v>2.379756435094268</v>
+        <v>11.6651262218606</v>
       </c>
       <c r="D2" t="n">
-        <v>13.88682127657113</v>
+        <v>11.06724186997429</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.219731559302038</v>
+        <v>2.012582793705961</v>
       </c>
       <c r="C2" t="n">
-        <v>3.855323234577225</v>
+        <v>4.187153958612646</v>
       </c>
       <c r="D2" t="n">
-        <v>6.687665361329272</v>
+        <v>6.799584599613409</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.67436286182632</v>
+        <v>11.97241325328985</v>
       </c>
       <c r="C3" t="n">
-        <v>25.56471021858694</v>
+        <v>35.76997760423254</v>
       </c>
       <c r="D3" t="n">
-        <v>71.92774555164256</v>
+        <v>57.1278989101219</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.17329598422873</v>
+        <v>38.63275390981624</v>
       </c>
       <c r="C4" t="n">
-        <v>100.3149804199391</v>
+        <v>144.7675347205304</v>
       </c>
       <c r="D4" t="n">
-        <v>180.9881345210122</v>
+        <v>129.2225415714864</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.80862561759666</v>
+        <v>30.99868376159304</v>
       </c>
       <c r="C5" t="n">
-        <v>265.2436859948821</v>
+        <v>317.0308773939013</v>
       </c>
       <c r="D5" t="n">
-        <v>170.9959063871882</v>
+        <v>126.8172596960817</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.7912318963607</v>
+        <v>16.7446888436336</v>
       </c>
       <c r="C6" t="n">
-        <v>273.9930215351296</v>
+        <v>311.9905846802982</v>
       </c>
       <c r="D6" t="n">
-        <v>90.48572240502003</v>
+        <v>72.33222560579226</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.569454726192155</v>
+        <v>5.030475236560656</v>
       </c>
       <c r="C7" t="n">
-        <v>160.8554343500229</v>
+        <v>200.5602567528767</v>
       </c>
       <c r="D7" t="n">
-        <v>33.95570784678443</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>79.35957567279091</v>
+        <v>102.2244797046991</v>
       </c>
       <c r="D8" t="n">
-        <v>24.70077223884975</v>
+        <v>24.20008090968387</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>33.17030968338697</v>
+        <v>39.04999668412111</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>20.41249826669968</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.78007281871549</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>19.07535789351553</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>15.28188476430585</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.789366211943441</v>
+        <v>6.370560852857552</v>
       </c>
       <c r="C2" t="n">
-        <v>5.475206946584461</v>
+        <v>8.348782476914876</v>
       </c>
       <c r="D2" t="n">
-        <v>13.93689040948772</v>
+        <v>16.55521153671396</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.88758204009713</v>
+        <v>12.47310458245573</v>
       </c>
       <c r="C3" t="n">
-        <v>5.993569734426778</v>
+        <v>29.3935262651495</v>
       </c>
       <c r="D3" t="n">
-        <v>14.79984664152067</v>
+        <v>12.43383467428585</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39832970268153</v>
+        <v>13.39709244739284</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14419667874446</v>
+        <v>70.1377192834096</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576274082668415</v>
+        <v>1.576128523222687</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.233296100712247</v>
+        <v>4.179299976978672</v>
       </c>
       <c r="C2" t="n">
-        <v>4.82921695719006</v>
+        <v>4.888121819444869</v>
       </c>
       <c r="D2" t="n">
-        <v>30.51860913421634</v>
+        <v>16.5139781331356</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.35100801423063</v>
+        <v>18.20160243673586</v>
       </c>
       <c r="C3" t="n">
-        <v>15.76195939168254</v>
+        <v>31.37174788920683</v>
       </c>
       <c r="D3" t="n">
-        <v>22.92871763268426</v>
+        <v>23.33614292994668</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.72443199474291</v>
+        <v>14.52397553662731</v>
       </c>
       <c r="C4" t="n">
-        <v>9.827294519510573</v>
+        <v>45.33318199130072</v>
       </c>
       <c r="D4" t="n">
-        <v>22.83250635766807</v>
+        <v>21.58175978245763</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44376274800173</v>
+        <v>15.43695089090866</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15993954148335</v>
+        <v>86.12193654927989</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251318473263523</v>
+        <v>3.249884398086034</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.286310476741575</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C2" t="n">
-        <v>7.478954010952201</v>
+        <v>5.864960785170445</v>
       </c>
       <c r="D2" t="n">
-        <v>34.67729240940584</v>
+        <v>18.6826588118168</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.39871274111122</v>
+        <v>16.09575361112645</v>
       </c>
       <c r="C3" t="n">
-        <v>17.59782759862408</v>
+        <v>23.98900515327081</v>
       </c>
       <c r="D3" t="n">
-        <v>42.02371048028472</v>
+        <v>31.13121970166636</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.38130332434203</v>
+        <v>26.30396623988479</v>
       </c>
       <c r="C4" t="n">
-        <v>27.26117025152543</v>
+        <v>64.11990605976767</v>
       </c>
       <c r="D4" t="n">
-        <v>29.18834099496192</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.53553552490002</v>
+        <v>12.7136327699962</v>
       </c>
       <c r="C5" t="n">
-        <v>12.61545799957152</v>
+        <v>50.06913291658734</v>
       </c>
       <c r="D5" t="n">
-        <v>30.63052837250049</v>
+        <v>30.43417883165113</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.45733986592554</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74035339319731</v>
+        <v>16.72551391086857</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1161556985036</v>
+        <v>102.0256348562983</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022106017959192</v>
+        <v>4.181378477717144</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.516039439535327</v>
+        <v>5.682355712180538</v>
       </c>
       <c r="C2" t="n">
-        <v>9.355073873767855</v>
+        <v>6.487388829662923</v>
       </c>
       <c r="D2" t="n">
-        <v>27.75400759905733</v>
+        <v>29.30418722406304</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.01092239793373</v>
+        <v>14.18625432636641</v>
       </c>
       <c r="C3" t="n">
-        <v>24.18535469412017</v>
+        <v>23.26251185212817</v>
       </c>
       <c r="D3" t="n">
-        <v>59.02758071783948</v>
+        <v>38.40597019013522</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.78894960578271</v>
+        <v>28.71612034921921</v>
       </c>
       <c r="C4" t="n">
-        <v>36.37375244234432</v>
+        <v>61.23553130469055</v>
       </c>
       <c r="D4" t="n">
-        <v>42.6147225982413</v>
+        <v>37.12675293150163</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.58648859452962</v>
+        <v>26.08994524035899</v>
       </c>
       <c r="C5" t="n">
-        <v>33.35487825178539</v>
+        <v>86.98284659626741</v>
       </c>
       <c r="D5" t="n">
-        <v>34.3366259560322</v>
+        <v>33.37942194439156</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.74719211838983</v>
+        <v>11.47172192412398</v>
       </c>
       <c r="C6" t="n">
-        <v>16.38242394076653</v>
+        <v>46.97368240509714</v>
       </c>
       <c r="D6" t="n">
-        <v>38.44033135978387</v>
+        <v>38.31957639216151</v>
       </c>
     </row>
     <row r="7">
@@ -5521,7 +5521,7 @@
         <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>9.82238578098934</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5588,10 +5588,10 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07029499594481</v>
+        <v>18.04404506210356</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8871625925923</v>
+        <v>117.7159130241994</v>
       </c>
       <c r="D21" t="n">
-        <v>6.883921903217068</v>
+        <v>6.014681687367852</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.077018289287756</v>
+        <v>7.536877125502762</v>
       </c>
       <c r="C2" t="n">
-        <v>8.259443435828414</v>
+        <v>11.06920536538279</v>
       </c>
       <c r="D2" t="n">
-        <v>33.68278198500381</v>
+        <v>23.83487076370406</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.66101930459437</v>
+        <v>15.15327581504952</v>
       </c>
       <c r="C3" t="n">
-        <v>29.42788743479814</v>
+        <v>22.83545160078081</v>
       </c>
       <c r="D3" t="n">
-        <v>63.02820261264523</v>
+        <v>49.04320656564941</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.56074217004095</v>
+        <v>20.15233512507428</v>
       </c>
       <c r="C4" t="n">
-        <v>42.02763747110171</v>
+        <v>49.74908316500287</v>
       </c>
       <c r="D4" t="n">
-        <v>53.37369568908209</v>
+        <v>41.37673874318607</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.58586669972387</v>
+        <v>21.08303194870026</v>
       </c>
       <c r="C5" t="n">
-        <v>38.55814108429348</v>
+        <v>74.17103905584653</v>
       </c>
       <c r="D5" t="n">
-        <v>34.01755795215198</v>
+        <v>31.26866438026092</v>
       </c>
     </row>
     <row r="6">
@@ -5812,10 +5812,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.79373517111693</v>
+        <v>12.7597749120958</v>
       </c>
       <c r="C6" t="n">
-        <v>23.90948358922682</v>
+        <v>63.4366096576119</v>
       </c>
       <c r="D6" t="n">
         <v>31.27553661419064</v>
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.389794896314989</v>
+        <v>5.569454726192155</v>
       </c>
       <c r="C7" t="n">
-        <v>14.55244622005047</v>
+        <v>28.20659329071511</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20092378866788</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.18749811597791</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
         <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.064815248714824</v>
+        <v>7.048623857562372</v>
       </c>
       <c r="C21" t="n">
-        <v>66.23264295670147</v>
+        <v>66.08084866464723</v>
       </c>
       <c r="D21" t="n">
-        <v>5.298611436536118</v>
+        <v>4.405389910976482</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.817435984739099</v>
+        <v>5.30634634145401</v>
       </c>
       <c r="C2" t="n">
-        <v>5.513495107050087</v>
+        <v>9.957866964175397</v>
       </c>
       <c r="D2" t="n">
-        <v>28.57573042751191</v>
+        <v>19.20396684277186</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.34886459237289</v>
+        <v>21.87333885061894</v>
       </c>
       <c r="C3" t="n">
-        <v>31.31284302695202</v>
+        <v>36.22158154818607</v>
       </c>
       <c r="D3" t="n">
-        <v>76.83157533435538</v>
+        <v>57.21134746498288</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.61928717939726</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="C4" t="n">
-        <v>62.33312523803848</v>
+        <v>53.96078081622169</v>
       </c>
       <c r="D4" t="n">
-        <v>75.08308267309181</v>
+        <v>57.07488453409257</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.21266370338984</v>
+        <v>26.43355693684537</v>
       </c>
       <c r="C5" t="n">
-        <v>62.90548414961439</v>
+        <v>85.21570072862315</v>
       </c>
       <c r="D5" t="n">
-        <v>46.80482179996669</v>
+        <v>40.05530633326987</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.48809283992669</v>
+        <v>21.89690079552086</v>
       </c>
       <c r="C6" t="n">
-        <v>46.249152599363</v>
+        <v>95.59768270103318</v>
       </c>
       <c r="D6" t="n">
-        <v>35.22019888985433</v>
+        <v>34.65667570761666</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.42027013287564</v>
+        <v>11.0191362324662</v>
       </c>
       <c r="C7" t="n">
-        <v>26.4698816019025</v>
+        <v>65.15663163545231</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>33.0574086973986</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>19.44351328260808</v>
+        <v>29.70768553050848</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6238,7 +6238,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.289035031616386</v>
+        <v>7.267487397321315</v>
       </c>
       <c r="C21" t="n">
-        <v>75.62373845302001</v>
+        <v>75.40018174720866</v>
       </c>
       <c r="D21" t="n">
-        <v>6.377905652664338</v>
+        <v>5.450615547990987</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.683517386334032</v>
+        <v>4.638757902566179</v>
       </c>
       <c r="C2" t="n">
-        <v>5.069745144730529</v>
+        <v>6.804493338134643</v>
       </c>
       <c r="D2" t="n">
-        <v>22.34065075784042</v>
+        <v>21.53365414494954</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.60764507566654</v>
+        <v>19.87548227247668</v>
       </c>
       <c r="C3" t="n">
-        <v>25.33399950808894</v>
+        <v>37.70402058159875</v>
       </c>
       <c r="D3" t="n">
-        <v>81.86303231862028</v>
+        <v>59.29756133650734</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.82196917482861</v>
+        <v>35.00814138573701</v>
       </c>
       <c r="C4" t="n">
-        <v>71.24150390637404</v>
+        <v>75.22347259479911</v>
       </c>
       <c r="D4" t="n">
-        <v>96.72865605632549</v>
+        <v>72.93894568701677</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.42221793275092</v>
+        <v>33.47759671481624</v>
       </c>
       <c r="C5" t="n">
-        <v>93.31511928865933</v>
+        <v>93.41329405908402</v>
       </c>
       <c r="D5" t="n">
-        <v>62.70913460876503</v>
+        <v>51.54175447295756</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.6591789823729</v>
+        <v>29.34345713223292</v>
       </c>
       <c r="C6" t="n">
-        <v>76.27688788145595</v>
+        <v>116.448040443827</v>
       </c>
       <c r="D6" t="n">
-        <v>42.2642386678252</v>
+        <v>39.16486116551801</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.1456428175938</v>
+        <v>19.10382857693868</v>
       </c>
       <c r="C7" t="n">
-        <v>48.80758711663017</v>
+        <v>105.1608870881013</v>
       </c>
       <c r="D7" t="n">
-        <v>36.4110588551057</v>
+        <v>35.93196597543326</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>9.095892479846697</v>
       </c>
       <c r="C8" t="n">
-        <v>28.12216298814988</v>
+        <v>60.16640805476577</v>
       </c>
       <c r="D8" t="n">
-        <v>34.71459882216722</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>24.51718541815559</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6605,7 +6605,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.500820778200025</v>
+        <v>7.472840253273474</v>
       </c>
       <c r="C21" t="n">
-        <v>85.32183635202529</v>
+        <v>84.06945284932659</v>
       </c>
       <c r="D21" t="n">
-        <v>7.500820778200025</v>
+        <v>6.53873522161429</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_73_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_73_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497649115302</v>
+        <v>10.84497619733136</v>
       </c>
       <c r="C21" t="n">
-        <v>37.7890724957252</v>
+        <v>37.78907147191032</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.862596379134452</v>
+        <v>0.7667449570167589</v>
       </c>
       <c r="C2" t="n">
-        <v>10.10414737210817</v>
+        <v>2.14217349066654</v>
       </c>
       <c r="D2" t="n">
-        <v>18.05924901962008</v>
+        <v>12.25417484440869</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.64691498383642</v>
+        <v>8.035604959260143</v>
       </c>
       <c r="C3" t="n">
-        <v>31.43556148998287</v>
+        <v>30.26728172192917</v>
       </c>
       <c r="D3" t="n">
-        <v>62.17899084847173</v>
+        <v>62.27225688037518</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.36098972218912</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="C4" t="n">
-        <v>84.54025830810133</v>
+        <v>107.5259173076319</v>
       </c>
       <c r="D4" t="n">
-        <v>84.75722455073988</v>
+        <v>74.52152298626264</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.90237467558562</v>
+        <v>17.15604113171301</v>
       </c>
       <c r="C5" t="n">
-        <v>117.048870038826</v>
+        <v>142.5006792714246</v>
       </c>
       <c r="D5" t="n">
-        <v>63.93631923907354</v>
+        <v>44.86587008407924</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.0315234041897</v>
+        <v>11.47172192412398</v>
       </c>
       <c r="C6" t="n">
-        <v>132.8707160404676</v>
+        <v>105.4190867343183</v>
       </c>
       <c r="D6" t="n">
-        <v>46.00764266411829</v>
+        <v>29.3032054763588</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.88908787161589</v>
+        <v>5.988660995905543</v>
       </c>
       <c r="C7" t="n">
-        <v>136.0623778269739</v>
+        <v>55.81432048183967</v>
       </c>
       <c r="D7" t="n">
-        <v>38.68675003354981</v>
+        <v>29.04500583014188</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.85384276525424</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>99.88792016859172</v>
+        <v>30.79251674370121</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.543749359432489</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>52.02968308196819</v>
+        <v>31.06249736236907</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.274128593663113</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>37.72365553568369</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.04125876577415</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.25358797846125</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.662904218537534</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92.9127136497676</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.662904218537534</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.614615120587509</v>
+        <v>0.7294385442553801</v>
       </c>
       <c r="C2" t="n">
-        <v>11.52866329097029</v>
+        <v>2.432770811123596</v>
       </c>
       <c r="D2" t="n">
-        <v>22.24345773511998</v>
+        <v>18.80439552714341</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.99405276051229</v>
+        <v>5.203262832508095</v>
       </c>
       <c r="C3" t="n">
-        <v>35.19074645872691</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D3" t="n">
-        <v>61.82065293642165</v>
+        <v>57.73167374823369</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.52315801983909</v>
+        <v>16.32351907851172</v>
       </c>
       <c r="C4" t="n">
-        <v>81.45168003054087</v>
+        <v>89.78573629189205</v>
       </c>
       <c r="D4" t="n">
-        <v>94.72490899195775</v>
+        <v>88.19039627249097</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.81111319681967</v>
+        <v>21.74571164906685</v>
       </c>
       <c r="C5" t="n">
-        <v>134.0085616296896</v>
+        <v>174.2111301185965</v>
       </c>
       <c r="D5" t="n">
-        <v>76.57632093125122</v>
+        <v>60.50020227420971</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.249152599363</v>
+        <v>16.90569546713008</v>
       </c>
       <c r="C6" t="n">
-        <v>157.665736058925</v>
+        <v>168.131166586196</v>
       </c>
       <c r="D6" t="n">
-        <v>54.42023874180921</v>
+        <v>36.10573531908495</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.97378021608837</v>
+        <v>9.402197763571703</v>
       </c>
       <c r="C7" t="n">
-        <v>161.2147540097772</v>
+        <v>103.8433816690021</v>
       </c>
       <c r="D7" t="n">
-        <v>42.27994663109313</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.11248437982766</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>137.6066669657542</v>
+        <v>51.7381040138069</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21943812632832</v>
+        <v>31.79389940203295</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>83.86874287839649</v>
+        <v>35.72187196672443</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>45.69544689416779</v>
+        <v>34.16482010778901</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>38.57777603837842</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>38.38240824523329</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>28.42257778564941</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>36.94316611080748</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.2949348885641</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>45.7376620454504</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.837362693330741</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100.9060446766333</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.817033029997084</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.874197425136166</v>
+        <v>0.3946625771072178</v>
       </c>
       <c r="C2" t="n">
-        <v>15.23279737909351</v>
+        <v>1.030835089459151</v>
       </c>
       <c r="D2" t="n">
-        <v>20.14840813425729</v>
+        <v>12.82457026057608</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.43093048890212</v>
+        <v>4.594579255875073</v>
       </c>
       <c r="C3" t="n">
-        <v>39.20609456909637</v>
+        <v>14.84402528821177</v>
       </c>
       <c r="D3" t="n">
-        <v>63.7890570834365</v>
+        <v>60.60819452167684</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.7491399182651</v>
+        <v>17.65084197465341</v>
       </c>
       <c r="C4" t="n">
-        <v>83.21293541195965</v>
+        <v>80.55828961967627</v>
       </c>
       <c r="D4" t="n">
-        <v>100.429844901336</v>
+        <v>96.26919813073798</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.50462798664542</v>
+        <v>21.81934272688536</v>
       </c>
       <c r="C5" t="n">
-        <v>140.5617275555371</v>
+        <v>196.2759097715436</v>
       </c>
       <c r="D5" t="n">
-        <v>89.43721585688444</v>
+        <v>68.15783436733483</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.25294072145974</v>
+        <v>13.32329809433347</v>
       </c>
       <c r="C6" t="n">
-        <v>179.2003719515788</v>
+        <v>209.6708754482871</v>
       </c>
       <c r="D6" t="n">
-        <v>62.71207985187777</v>
+        <v>36.91076843656734</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.93869934064274</v>
+        <v>4.311835917051991</v>
       </c>
       <c r="C7" t="n">
-        <v>188.2835017112703</v>
+        <v>96.89653491375168</v>
       </c>
       <c r="D7" t="n">
-        <v>47.13076203777662</v>
+        <v>32.93763547748049</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.78836876870596</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>170.7357432455628</v>
+        <v>44.06083696659685</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.97656122828509</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>118.9249899016416</v>
+        <v>26.07031028627404</v>
       </c>
       <c r="D9" t="n">
-        <v>37.05312185368311</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.971791358484101</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>67.04845946153593</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>41.04785326226338</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>43.44429940832985</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>39.59388491227386</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.995446662313685</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107.9385299412347</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.994308327892107</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.308710747490003</v>
+        <v>0.3809181092477624</v>
       </c>
       <c r="C2" t="n">
-        <v>10.6018934581613</v>
+        <v>5.836490101747288</v>
       </c>
       <c r="D2" t="n">
-        <v>16.73094437577414</v>
+        <v>15.58524480491811</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.56899706230243</v>
+        <v>2.940334374219197</v>
       </c>
       <c r="C3" t="n">
-        <v>59.07666810305182</v>
+        <v>8.821003122657592</v>
       </c>
       <c r="D3" t="n">
-        <v>70.03788122096745</v>
+        <v>57.45678439104458</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.7769476491535</v>
+        <v>13.38809344281375</v>
       </c>
       <c r="C4" t="n">
-        <v>114.9027695573424</v>
+        <v>57.89169862402591</v>
       </c>
       <c r="D4" t="n">
-        <v>97.69862278812133</v>
+        <v>103.9268302238631</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.99239236474006</v>
+        <v>24.66641106920112</v>
       </c>
       <c r="C5" t="n">
-        <v>107.0595871481147</v>
+        <v>173.8184310368978</v>
       </c>
       <c r="D5" t="n">
-        <v>61.50649367106269</v>
+        <v>85.16661334341082</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.64659618866693</v>
+        <v>20.16607959293373</v>
       </c>
       <c r="C6" t="n">
-        <v>124.0153517481614</v>
+        <v>261.313749934782</v>
       </c>
       <c r="D6" t="n">
-        <v>31.03402667894593</v>
+        <v>48.26173539306896</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.38518925743002</v>
+        <v>8.444012004226815</v>
       </c>
       <c r="C7" t="n">
-        <v>120.0726529679061</v>
+        <v>193.5535233876672</v>
       </c>
       <c r="D7" t="n">
-        <v>28.14670668075605</v>
+        <v>35.93196597543326</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>87.62098260402782</v>
+        <v>81.86303231862027</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>36.88426124855267</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>51.14218315732908</v>
+        <v>38.2734342500619</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>41.3796839862988</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>31.60245859970483</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>31.62994753542373</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>31.02617269731195</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>20.58823110575986</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>46.74984392852887</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.902447124381071</v>
+        <v>0.2631083847381452</v>
       </c>
       <c r="C2" t="n">
-        <v>5.210135066437823</v>
+        <v>3.861213720802705</v>
       </c>
       <c r="D2" t="n">
-        <v>12.76566539832127</v>
+        <v>11.45405046544754</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.15313694632928</v>
+        <v>2.233476027161494</v>
       </c>
       <c r="C3" t="n">
-        <v>51.2619563772472</v>
+        <v>16.07611865704152</v>
       </c>
       <c r="D3" t="n">
-        <v>68.52598975642736</v>
+        <v>57.48132808365075</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.15379989886403</v>
+        <v>10.60582044897829</v>
       </c>
       <c r="C4" t="n">
-        <v>133.2810865808427</v>
+        <v>42.24460371374025</v>
       </c>
       <c r="D4" t="n">
-        <v>107.8194598712017</v>
+        <v>108.3044432370996</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.45305302221007</v>
+        <v>24.83821691744431</v>
       </c>
       <c r="C5" t="n">
-        <v>155.8769917417874</v>
+        <v>151.066427990978</v>
       </c>
       <c r="D5" t="n">
-        <v>77.16536955379931</v>
+        <v>98.51838212116745</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.87931145230244</v>
+        <v>24.43275511559037</v>
       </c>
       <c r="C6" t="n">
-        <v>147.6833254021435</v>
+        <v>283.0496441068065</v>
       </c>
       <c r="D6" t="n">
-        <v>37.59504658642736</v>
+        <v>57.3586096206199</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.24734366820796</v>
+        <v>9.282424543653592</v>
       </c>
       <c r="C7" t="n">
-        <v>147.6204935490717</v>
+        <v>262.1835784007447</v>
       </c>
       <c r="D7" t="n">
-        <v>30.60205768907732</v>
+        <v>39.28561613314036</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>112.4886519525995</v>
+        <v>126.0907663949391</v>
       </c>
       <c r="D8" t="n">
-        <v>28.03871443328891</v>
+        <v>39.63806355896497</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>56.57812019574367</v>
+        <v>50.69843319500952</v>
       </c>
       <c r="D9" t="n">
-        <v>28.17812260729194</v>
+        <v>41.3796839862988</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>33.88011327355743</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>32.59893251951534</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>22.99842171968578</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.09163099832699</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.77972866135022</v>
+        <v>0.9866564427680444</v>
       </c>
       <c r="C2" t="n">
-        <v>14.25497666566369</v>
+        <v>3.681553890925539</v>
       </c>
       <c r="D2" t="n">
-        <v>19.19120412261665</v>
+        <v>12.9885221271853</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.87762569433442</v>
+        <v>1.570796326794897</v>
       </c>
       <c r="C3" t="n">
-        <v>35.23001636689679</v>
+        <v>15.43798264928109</v>
       </c>
       <c r="D3" t="n">
-        <v>63.27854827722817</v>
+        <v>53.58869843631214</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.08020987877453</v>
+        <v>7.58105577219387</v>
       </c>
       <c r="C4" t="n">
-        <v>130.4988135870073</v>
+        <v>41.555416825359</v>
       </c>
       <c r="D4" t="n">
-        <v>116.0131262108456</v>
+        <v>111.7248522386955</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.46625771072178</v>
+        <v>21.50027472300515</v>
       </c>
       <c r="C5" t="n">
-        <v>200.3992501293802</v>
+        <v>116.4107340310656</v>
       </c>
       <c r="D5" t="n">
-        <v>94.81228453763572</v>
+        <v>112.3610247510475</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.75605320992383</v>
+        <v>28.49817235887642</v>
       </c>
       <c r="C6" t="n">
-        <v>192.9261866046535</v>
+        <v>265.1376572428234</v>
       </c>
       <c r="D6" t="n">
-        <v>49.87180162803373</v>
+        <v>71.60769580005812</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.45180923259856</v>
+        <v>16.82813739849458</v>
       </c>
       <c r="C7" t="n">
-        <v>179.360396827371</v>
+        <v>331.5921593432899</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>45.15450390912779</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.35038611942487</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>150.04050164004</v>
+        <v>221.0552218267331</v>
       </c>
       <c r="D8" t="n">
-        <v>29.54078842078653</v>
+        <v>41.14013754646259</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>90.74686729434964</v>
+        <v>93.52030455884689</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>42.26718391093791</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>47.40368789955724</v>
+        <v>43.13308538608361</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>33.40691088011046</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.295326132529043</v>
+        <v>0.6705336820005715</v>
       </c>
       <c r="C2" t="n">
-        <v>6.87321567743192</v>
+        <v>1.943860454408685</v>
       </c>
       <c r="D2" t="n">
-        <v>13.38416645199677</v>
+        <v>9.351146882950868</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.48492661263569</v>
+        <v>2.748893571891069</v>
       </c>
       <c r="C3" t="n">
-        <v>45.46473618366979</v>
+        <v>17.45547418150829</v>
       </c>
       <c r="D3" t="n">
-        <v>65.25676990128549</v>
+        <v>58.69869523691679</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.65377152223292</v>
+        <v>13.92412768933251</v>
       </c>
       <c r="C4" t="n">
-        <v>129.2353042916416</v>
+        <v>61.74604011089889</v>
       </c>
       <c r="D4" t="n">
-        <v>122.7135542923301</v>
+        <v>114.7879050759456</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.54618018539328</v>
+        <v>17.42602175038089</v>
       </c>
       <c r="C5" t="n">
-        <v>240.9208866221673</v>
+        <v>200.3992501293802</v>
       </c>
       <c r="D5" t="n">
-        <v>99.79465413668829</v>
+        <v>104.0161692649496</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.79251674370121</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="C6" t="n">
-        <v>228.5891537091231</v>
+        <v>283.3716573537994</v>
       </c>
       <c r="D6" t="n">
-        <v>49.02651685467723</v>
+        <v>61.06176196103888</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.144578954431539</v>
+        <v>4.19206269713388</v>
       </c>
       <c r="C7" t="n">
-        <v>189.8405535702057</v>
+        <v>155.4656394537079</v>
       </c>
       <c r="D7" t="n">
-        <v>33.89582123682538</v>
+        <v>35.51275970571987</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>110.9865779651019</v>
+        <v>68.92850631516855</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.109374905798895</v>
       </c>
       <c r="C9" t="n">
-        <v>36.16562192904399</v>
+        <v>32.8374972116473</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>26.5140602485936</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>26.05067533218912</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.72429312602266</v>
+        <v>20.7904711328347</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>13.78864650614645</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>34.40043955680824</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.493639168786898</v>
+        <v>0.3563744166415922</v>
       </c>
       <c r="C2" t="n">
-        <v>9.874418409314419</v>
+        <v>1.990984344212531</v>
       </c>
       <c r="D2" t="n">
-        <v>12.04113559258713</v>
+        <v>6.631705742187204</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.90507357232432</v>
+        <v>2.513274122871834</v>
       </c>
       <c r="C3" t="n">
-        <v>36.16267668593126</v>
+        <v>12.03131811554466</v>
       </c>
       <c r="D3" t="n">
-        <v>61.18742566718246</v>
+        <v>52.76893910326606</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.01188845010475</v>
+        <v>9.074294030353268</v>
       </c>
       <c r="C4" t="n">
-        <v>122.7007915721749</v>
+        <v>50.64247357586746</v>
       </c>
       <c r="D4" t="n">
-        <v>126.1850141745468</v>
+        <v>112.9117852131299</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.30198704894308</v>
+        <v>15.51161372709961</v>
       </c>
       <c r="C5" t="n">
-        <v>241.4853915521092</v>
+        <v>142.3534171157875</v>
       </c>
       <c r="D5" t="n">
-        <v>116.3616466458532</v>
+        <v>108.826733015759</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.48687441251096</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>295.9301739865246</v>
+        <v>252.6193922659723</v>
       </c>
       <c r="D6" t="n">
-        <v>64.24164277509429</v>
+        <v>64.32214608684252</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.00779722837174</v>
+        <v>3.593196597543325</v>
       </c>
       <c r="C7" t="n">
-        <v>250.8650091184832</v>
+        <v>195.1704618565616</v>
       </c>
       <c r="D7" t="n">
-        <v>38.08788393395925</v>
+        <v>34.07548106670254</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C8" t="n">
-        <v>165.7288299539041</v>
+        <v>81.77958376375931</v>
       </c>
       <c r="D8" t="n">
-        <v>32.87873061522568</v>
+        <v>26.78698611037422</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>70.66718149938963</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>20.96718571959912</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>17.93653055658923</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>13.32722508515045</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.41424077792992</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.68664255589602</v>
+        <v>0.3200497515844601</v>
       </c>
       <c r="C2" t="n">
-        <v>6.365652114336318</v>
+        <v>9.679050616169304</v>
       </c>
       <c r="D2" t="n">
-        <v>9.262789589568657</v>
+        <v>6.462845137056753</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.20665004397734</v>
+        <v>1.811324514335365</v>
       </c>
       <c r="C3" t="n">
-        <v>37.8120128290659</v>
+        <v>9.429686699290613</v>
       </c>
       <c r="D3" t="n">
-        <v>57.84457473422207</v>
+        <v>45.82798283424111</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.91505528028281</v>
+        <v>6.840818003191774</v>
       </c>
       <c r="C4" t="n">
-        <v>111.4823605557466</v>
+        <v>39.10497455555895</v>
       </c>
       <c r="D4" t="n">
-        <v>127.665489712551</v>
+        <v>114.1370063480299</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.44987109938586</v>
+        <v>14.99619618237003</v>
       </c>
       <c r="C5" t="n">
-        <v>243.8170423496954</v>
+        <v>115.2080930933632</v>
       </c>
       <c r="D5" t="n">
-        <v>128.3880560228766</v>
+        <v>125.271007061893</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.56487444950297</v>
+        <v>15.77864910265474</v>
       </c>
       <c r="C6" t="n">
-        <v>337.3491278809933</v>
+        <v>242.3149683621978</v>
       </c>
       <c r="D6" t="n">
-        <v>74.42531171124647</v>
+        <v>83.15992103593032</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.09142570968197</v>
+        <v>7.72537268471815</v>
       </c>
       <c r="C7" t="n">
-        <v>310.6318458576205</v>
+        <v>287.2760679735889</v>
       </c>
       <c r="D7" t="n">
-        <v>42.27994663109313</v>
+        <v>43.95677170994669</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.339324852770902</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>208.6213871524472</v>
+        <v>171.1529860198677</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>29.70768553050848</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>77.21249344360311</v>
+        <v>67.00624431025328</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>23.07499804061703</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>20.4988920646734</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>16.8811517745239</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>18.12502611580461</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>13.4519070435898</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.75478405811655</v>
+        <v>0.1757328390601791</v>
       </c>
       <c r="C2" t="n">
-        <v>7.071528713689775</v>
+        <v>13.07197068204628</v>
       </c>
       <c r="D2" t="n">
-        <v>9.140071126537803</v>
+        <v>13.03171902617216</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.659014751456867</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C3" t="n">
-        <v>31.74481201682061</v>
+        <v>25.0689276279423</v>
       </c>
       <c r="D3" t="n">
-        <v>52.94074495150925</v>
+        <v>40.72780351067893</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.50366193447439</v>
+        <v>5.117850782238622</v>
       </c>
       <c r="C4" t="n">
-        <v>103.8502539029318</v>
+        <v>30.71986741358695</v>
       </c>
       <c r="D4" t="n">
-        <v>126.8359129024624</v>
+        <v>110.4358175030195</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.66447293598841</v>
+        <v>12.98361338866407</v>
       </c>
       <c r="C5" t="n">
-        <v>227.4218556887737</v>
+        <v>92.82424543653593</v>
       </c>
       <c r="D5" t="n">
-        <v>137.8619213688584</v>
+        <v>137.7392029058275</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.17872880656449</v>
+        <v>18.19374845510189</v>
       </c>
       <c r="C6" t="n">
-        <v>357.4347041621788</v>
+        <v>214.1388092503143</v>
       </c>
       <c r="D6" t="n">
-        <v>90.44547074914593</v>
+        <v>101.957444329144</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.008861091534</v>
+        <v>12.87562114119692</v>
       </c>
       <c r="C7" t="n">
-        <v>377.9443954515988</v>
+        <v>318.776424812052</v>
       </c>
       <c r="D7" t="n">
-        <v>49.88554609589318</v>
+        <v>55.57477404200344</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.593818492349078</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C8" t="n">
-        <v>285.2271605148258</v>
+        <v>276.548510809284</v>
       </c>
       <c r="D8" t="n">
-        <v>36.38356991938679</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>138.6718632248619</v>
+        <v>137.6734258096429</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>25.18281036163492</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>51.24723016168351</v>
+        <v>52.10135066437823</v>
       </c>
       <c r="D10" t="n">
-        <v>26.76244241776806</v>
+        <v>21.49536598448391</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>23.98900515327081</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>18.65811511921063</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.09302935219197</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.994731408580272</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.871833019100173</v>
+        <v>4.6475936319044</v>
       </c>
       <c r="C2" t="n">
-        <v>11.6651262218606</v>
+        <v>16.31566509687774</v>
       </c>
       <c r="D2" t="n">
-        <v>11.06724186997429</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.012582793705961</v>
+        <v>0.7991426312569037</v>
       </c>
       <c r="C2" t="n">
-        <v>4.187153958612646</v>
+        <v>11.8202423591316</v>
       </c>
       <c r="D2" t="n">
-        <v>6.799584599613409</v>
+        <v>12.82260676516759</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.97241325328985</v>
+        <v>1.001382658331747</v>
       </c>
       <c r="C3" t="n">
-        <v>35.76997760423254</v>
+        <v>37.89055264540564</v>
       </c>
       <c r="D3" t="n">
-        <v>57.1278989101219</v>
+        <v>41.31194339470579</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.63275390981624</v>
+        <v>3.943680527959437</v>
       </c>
       <c r="C4" t="n">
-        <v>144.7675347205304</v>
+        <v>46.29038600294135</v>
       </c>
       <c r="D4" t="n">
-        <v>129.2225415714864</v>
+        <v>106.3262216130423</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.99868376159304</v>
+        <v>10.70104997629023</v>
       </c>
       <c r="C5" t="n">
-        <v>317.0308773939013</v>
+        <v>74.76008767839463</v>
       </c>
       <c r="D5" t="n">
-        <v>126.8172596960817</v>
+        <v>143.6787765165207</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.7446888436336</v>
+        <v>18.23400011097601</v>
       </c>
       <c r="C6" t="n">
-        <v>311.9905846802982</v>
+        <v>184.7148488063332</v>
       </c>
       <c r="D6" t="n">
-        <v>72.33222560579226</v>
+        <v>119.5876696020082</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.030475236560656</v>
+        <v>16.70836417857646</v>
       </c>
       <c r="C7" t="n">
-        <v>200.5602567528767</v>
+        <v>315.4227746543449</v>
       </c>
       <c r="D7" t="n">
-        <v>31.4404702285041</v>
+        <v>69.10914789274997</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>8.92899537012474</v>
       </c>
       <c r="C8" t="n">
-        <v>102.2244797046991</v>
+        <v>347.0625396668112</v>
       </c>
       <c r="D8" t="n">
-        <v>24.20008090968387</v>
+        <v>39.47116644924301</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>39.04999668412111</v>
+        <v>229.973417972111</v>
       </c>
       <c r="D9" t="n">
-        <v>20.41249826669968</v>
+        <v>27.62343515439249</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>99.64739198105126</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>22.34948648717864</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.28188476430585</v>
+        <v>38.56010457970196</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>19.36890045708532</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.609305471438775</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.7166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.370560852857552</v>
+        <v>4.798782778358409</v>
       </c>
       <c r="C2" t="n">
-        <v>8.348782476914876</v>
+        <v>11.88307421220339</v>
       </c>
       <c r="D2" t="n">
-        <v>16.55521153671396</v>
+        <v>16.34708102341364</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.47310458245573</v>
+        <v>7.677267047210058</v>
       </c>
       <c r="C3" t="n">
-        <v>29.3935262651495</v>
+        <v>32.21114217633785</v>
       </c>
       <c r="D3" t="n">
-        <v>12.43383467428585</v>
+        <v>6.75933294373929</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39709244739284</v>
+        <v>11.6777159517073</v>
       </c>
       <c r="C21" t="n">
-        <v>70.1377192834096</v>
+        <v>59.94560855209747</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576128523222687</v>
+        <v>0.7785143967804866</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.179299976978672</v>
+        <v>3.221114217633785</v>
       </c>
       <c r="C2" t="n">
-        <v>4.888121819444869</v>
+        <v>4.344233591292136</v>
       </c>
       <c r="D2" t="n">
-        <v>16.5139781331356</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.20160243673586</v>
+        <v>13.37140373184156</v>
       </c>
       <c r="C3" t="n">
-        <v>31.37174788920683</v>
+        <v>42.02371048028472</v>
       </c>
       <c r="D3" t="n">
-        <v>23.33614292994668</v>
+        <v>19.44351328260808</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14.52397553662731</v>
+        <v>9.559277396251193</v>
       </c>
       <c r="C4" t="n">
-        <v>45.33318199130072</v>
+        <v>52.07189823325082</v>
       </c>
       <c r="D4" t="n">
-        <v>21.58175978245763</v>
+        <v>17.70189285527424</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.105088062083415</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43695089090866</v>
+        <v>13.62637312140532</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12193654927989</v>
+        <v>73.74272512760525</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249884398086034</v>
+        <v>1.603102720165332</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.68744437715102</v>
+        <v>2.051852701875834</v>
       </c>
       <c r="C2" t="n">
-        <v>5.864960785170445</v>
+        <v>6.14672237628928</v>
       </c>
       <c r="D2" t="n">
-        <v>18.6826588118168</v>
+        <v>23.9006478598886</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.09575361112645</v>
+        <v>12.14912784005428</v>
       </c>
       <c r="C3" t="n">
-        <v>23.98900515327081</v>
+        <v>26.09976271740146</v>
       </c>
       <c r="D3" t="n">
-        <v>31.13121970166636</v>
+        <v>35.17602024316322</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.30396623988479</v>
+        <v>19.16960567312322</v>
       </c>
       <c r="C4" t="n">
-        <v>64.11990605976767</v>
+        <v>85.02524167399926</v>
       </c>
       <c r="D4" t="n">
-        <v>28.42257778564941</v>
+        <v>23.7769476491535</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.7136327699962</v>
+        <v>9.007535186464487</v>
       </c>
       <c r="C5" t="n">
-        <v>50.06913291658734</v>
+        <v>59.71480411081225</v>
       </c>
       <c r="D5" t="n">
-        <v>30.43417883165113</v>
+        <v>26.53173170727006</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>10.54593383901924</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>31.55729820530948</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>29.45733986592554</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.95717262057418</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72551391086857</v>
+        <v>14.83069653940998</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0256348562983</v>
+        <v>87.33632406541432</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181378477717144</v>
+        <v>2.471782756568329</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.682355712180538</v>
+        <v>2.22856728864026</v>
       </c>
       <c r="C2" t="n">
-        <v>6.487388829662923</v>
+        <v>6.211517724769569</v>
       </c>
       <c r="D2" t="n">
-        <v>29.30418722406304</v>
+        <v>25.18968259556466</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.18625432636641</v>
+        <v>9.400234268163208</v>
       </c>
       <c r="C3" t="n">
-        <v>23.26251185212817</v>
+        <v>24.77931205518949</v>
       </c>
       <c r="D3" t="n">
-        <v>38.40597019013522</v>
+        <v>46.13232462255762</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.71612034921921</v>
+        <v>21.56899706230242</v>
       </c>
       <c r="C4" t="n">
-        <v>61.23553130469055</v>
+        <v>73.69194617617408</v>
       </c>
       <c r="D4" t="n">
-        <v>37.12675293150163</v>
+        <v>36.0419217183089</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.08994524035899</v>
+        <v>19.315886081056</v>
       </c>
       <c r="C5" t="n">
-        <v>86.98284659626741</v>
+        <v>114.2508890817226</v>
       </c>
       <c r="D5" t="n">
-        <v>33.37942194439156</v>
+        <v>29.20699420134261</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.47172192412398</v>
+        <v>8.45284773356504</v>
       </c>
       <c r="C6" t="n">
-        <v>46.97368240509714</v>
+        <v>55.58753676215866</v>
       </c>
       <c r="D6" t="n">
-        <v>38.31957639216151</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>25.70215489718149</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>27.62343515439249</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>36.72030938194344</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.82238578098934</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>32.5203927031756</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04404506210356</v>
+        <v>16.06278658464943</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7159130241994</v>
+        <v>100.6037686091201</v>
       </c>
       <c r="D21" t="n">
-        <v>6.014681687367852</v>
+        <v>3.381639280978828</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.536877125502762</v>
+        <v>1.699405276051229</v>
       </c>
       <c r="C2" t="n">
-        <v>11.06920536538279</v>
+        <v>8.977101007632834</v>
       </c>
       <c r="D2" t="n">
-        <v>23.83487076370406</v>
+        <v>19.98052927683108</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.15327581504952</v>
+        <v>8.423395302437633</v>
       </c>
       <c r="C3" t="n">
-        <v>22.83545160078081</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D3" t="n">
-        <v>49.04320656564941</v>
+        <v>55.01223260747002</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.15233512507428</v>
+        <v>19.85879256150448</v>
       </c>
       <c r="C4" t="n">
-        <v>49.74908316500287</v>
+        <v>67.25953521794898</v>
       </c>
       <c r="D4" t="n">
-        <v>41.37673874318607</v>
+        <v>50.24682925105601</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.08303194870026</v>
+        <v>25.89359569950963</v>
       </c>
       <c r="C5" t="n">
-        <v>74.17103905584653</v>
+        <v>125.8355119918349</v>
       </c>
       <c r="D5" t="n">
-        <v>31.26866438026092</v>
+        <v>35.2447425824605</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.7597749120958</v>
+        <v>16.86544381125596</v>
       </c>
       <c r="C6" t="n">
-        <v>63.4366096576119</v>
+        <v>119.50716629026</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>34.49566908412018</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.569454726192155</v>
+        <v>8.324238784308704</v>
       </c>
       <c r="C7" t="n">
-        <v>28.20659329071511</v>
+        <v>48.68781389671206</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>36.89015173477814</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>37.05115835827462</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>30.50780990946962</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>37.94062177832222</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>5.858088551240717</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.048623857562372</v>
+        <v>17.3164641613019</v>
       </c>
       <c r="C21" t="n">
-        <v>66.08084866464723</v>
+        <v>113.4228402565275</v>
       </c>
       <c r="D21" t="n">
-        <v>4.405389910976482</v>
+        <v>4.329116040325475</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.30634634145401</v>
+        <v>1.406844460185679</v>
       </c>
       <c r="C2" t="n">
-        <v>9.957866964175397</v>
+        <v>7.357217295625596</v>
       </c>
       <c r="D2" t="n">
-        <v>19.20396684277186</v>
+        <v>21.46198656253952</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.87333885061894</v>
+        <v>7.009678608322226</v>
       </c>
       <c r="C3" t="n">
-        <v>36.22158154818607</v>
+        <v>29.77149913128453</v>
       </c>
       <c r="D3" t="n">
-        <v>57.21134746498288</v>
+        <v>57.41751448287471</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.03594911662541</v>
+        <v>17.99543541884404</v>
       </c>
       <c r="C4" t="n">
-        <v>53.96078081622169</v>
+        <v>63.94122797759476</v>
       </c>
       <c r="D4" t="n">
-        <v>57.07488453409257</v>
+        <v>63.36690557061038</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.43355693684537</v>
+        <v>27.68528525976006</v>
       </c>
       <c r="C5" t="n">
-        <v>85.21570072862315</v>
+        <v>123.6511233498858</v>
       </c>
       <c r="D5" t="n">
-        <v>40.05530633326987</v>
+        <v>44.17864669110647</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.89690079552086</v>
+        <v>25.318291544821</v>
       </c>
       <c r="C6" t="n">
-        <v>95.59768270103318</v>
+        <v>158.3097625529109</v>
       </c>
       <c r="D6" t="n">
-        <v>34.65667570761666</v>
+        <v>37.27303333943441</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.0191362324662</v>
+        <v>13.65414707066464</v>
       </c>
       <c r="C7" t="n">
-        <v>65.15663163545231</v>
+        <v>106.3586192872825</v>
       </c>
       <c r="D7" t="n">
-        <v>33.0574086973986</v>
+        <v>38.74663664350886</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>8.511752595819845</v>
       </c>
       <c r="C8" t="n">
-        <v>29.70768553050848</v>
+        <v>43.89393985687489</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>31.61718481526852</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>39.160934174701</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>33.88011327355743</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>46.02335062738621</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.267487397321315</v>
+        <v>17.70118001472586</v>
       </c>
       <c r="C21" t="n">
-        <v>75.40018174720866</v>
+        <v>126.5634371052899</v>
       </c>
       <c r="D21" t="n">
-        <v>5.450615547990987</v>
+        <v>5.310354004417758</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.638757902566179</v>
+        <v>1.363647561198819</v>
       </c>
       <c r="C2" t="n">
-        <v>6.804493338134643</v>
+        <v>4.649557127312894</v>
       </c>
       <c r="D2" t="n">
-        <v>21.53365414494954</v>
+        <v>17.04608538883737</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.87548227247668</v>
+        <v>10.67159754516283</v>
       </c>
       <c r="C3" t="n">
-        <v>37.70402058159875</v>
+        <v>43.4914232981337</v>
       </c>
       <c r="D3" t="n">
-        <v>59.29756133650734</v>
+        <v>62.75331325545611</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.00814138573701</v>
+        <v>13.29875440172729</v>
       </c>
       <c r="C4" t="n">
-        <v>75.22347259479911</v>
+        <v>100.3915567408703</v>
       </c>
       <c r="D4" t="n">
-        <v>72.93894568701677</v>
+        <v>58.019325825578</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.47759671481624</v>
+        <v>14.25988540418492</v>
       </c>
       <c r="C5" t="n">
-        <v>93.41329405908402</v>
+        <v>94.59139130418019</v>
       </c>
       <c r="D5" t="n">
-        <v>51.54175447295756</v>
+        <v>34.97476196379262</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.34345713223292</v>
+        <v>8.45284773356504</v>
       </c>
       <c r="C6" t="n">
-        <v>116.448040443827</v>
+        <v>70.03788122096746</v>
       </c>
       <c r="D6" t="n">
-        <v>39.16486116551801</v>
+        <v>25.51954982419159</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.10382857693868</v>
+        <v>5.629341336151211</v>
       </c>
       <c r="C7" t="n">
-        <v>105.1608870881013</v>
+        <v>30.84160412891355</v>
       </c>
       <c r="D7" t="n">
-        <v>35.93196597543326</v>
+        <v>26.94897448157494</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.095892479846697</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>60.16640805476577</v>
+        <v>23.28214680621311</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>28.78975142703771</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>30.7296848906294</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>32.25041208450772</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>30.17205219461722</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.16709636949629</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.472840253273474</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.06945284932659</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.53873522161429</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
